--- a/data/4-reports/7_SNOMED_Matches_All.xlsx
+++ b/data/4-reports/7_SNOMED_Matches_All.xlsx
@@ -470,7 +470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K211"/>
+  <dimension ref="A1:K214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -534,7 +534,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Existing SNOMED (master)</t>
+          <t>Existing SNOMED (ontology)</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -852,7 +852,7 @@
       <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>363732003, 386584007</t>
+          <t>363732003</t>
         </is>
       </c>
       <c r="K7" s="5" t="inlineStr">
@@ -1040,7 +1040,7 @@
       <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>68225006, 19754005, 86166000</t>
+          <t>68225006</t>
         </is>
       </c>
       <c r="K11" s="5" t="inlineStr">
@@ -1166,47 +1166,23 @@
           <t>Anti-CASPR2 autoimmune encephalitis</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>763803004</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>Morvan syndrome</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>0.778</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
+      <c r="C14" s="2" t="inlineStr"/>
+      <c r="D14" s="3" t="inlineStr"/>
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr"/>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>Morvan syndrome</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>35622356</t>
-        </is>
-      </c>
+          <t>no match</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr"/>
       <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="3" t="inlineStr">
         <is>
           <t>763803004</t>
         </is>
       </c>
-      <c r="K14" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="K14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1252,7 +1228,7 @@
       <c r="I15" s="2" t="inlineStr"/>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>788613004, 236506009, 62853008, 50581000</t>
+          <t>788613004</t>
         </is>
       </c>
       <c r="K15" s="5" t="inlineStr">
@@ -1355,7 +1331,7 @@
       <c r="I18" s="2" t="inlineStr"/>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>722191003, 82275008, 195353004</t>
+          <t>722191003</t>
         </is>
       </c>
       <c r="K18" s="5" t="inlineStr">
@@ -1711,22 +1687,22 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001026</t>
+          <t>ARI:0001027</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune disease</t>
+          <t>Autoimmune disorder of inner ear</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>85828009</t>
+          <t>232308006</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune disease</t>
+          <t>Autoimmune disorder of inner ear</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1746,13 +1722,13 @@
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>434621</t>
+          <t>4337463</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr"/>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>85828009</t>
+          <t>13445001, 232308006</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
@@ -1764,22 +1740,22 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001027</t>
+          <t>ARI:0001028</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune disorder of inner ear</t>
+          <t>Autoimmune encephalitis</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>232308006</t>
+          <t>95643007</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune disorder of inner ear</t>
+          <t>Autoimmune encephalitis</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1799,13 +1775,13 @@
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>4337463</t>
+          <t>4318558</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr"/>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>232308006, 13445001</t>
+          <t>95643007</t>
         </is>
       </c>
       <c r="K28" s="5" t="inlineStr">
@@ -1817,22 +1793,22 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001028</t>
+          <t>ARI:0001029</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune encephalitis</t>
+          <t>Autoimmune encephalitis caused by N-methyl D-aspartate receptor antibody</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>95643007</t>
+          <t>452281000124106</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune encephalitis</t>
+          <t>Autoimmune encephalitis caused by N-methyl D-aspartate receptor antibody</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1852,13 +1828,13 @@
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>4318558</t>
+          <t>764228</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>95643007</t>
+          <t>452281000124106, 716684004</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
@@ -1870,22 +1846,22 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001029</t>
+          <t>ARI:0001030</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune encephalitis caused by N-methyl D-aspartate receptor antibody</t>
+          <t>Autoimmune ganglionopathy</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>452281000124106</t>
+          <t>838330008</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune encephalitis caused by N-methyl D-aspartate receptor antibody</t>
+          <t>Autoimmune ganglionopathy</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1905,13 +1881,13 @@
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>764228</t>
+          <t>3654638</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr"/>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>452281000124106, 716684004</t>
+          <t>838330008</t>
         </is>
       </c>
       <c r="K30" s="5" t="inlineStr">
@@ -1923,32 +1899,32 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001030</t>
+          <t>ARI:0001031</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune ganglionopathy</t>
+          <t>Autoimmune gastritis</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>838330008</t>
+          <t>84568007</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune ganglionopathy</t>
+          <t>Atrophic gastritis</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>0.778</t>
+          <t>0.556</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>synonym</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
@@ -1958,13 +1934,13 @@
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>3654638</t>
+          <t>192667</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>838330008, 838321000</t>
+          <t>235728001, 84027009, 84568007</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
@@ -1976,22 +1952,22 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001031</t>
+          <t>ARI:0001032</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune gastritis</t>
+          <t>Autoimmune hemolytic anemia</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>84568007</t>
+          <t>413603009</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Atrophic gastritis</t>
+          <t>Autoimmune hemolytic anemia</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -2006,18 +1982,18 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>Atrophic gastritis</t>
+          <t>(preferred name)</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>192667</t>
+          <t>441269</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>84568007, 235728001, 84027009</t>
+          <t>413603009, 718716008</t>
         </is>
       </c>
       <c r="K32" s="5" t="inlineStr">
@@ -2029,22 +2005,22 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001032</t>
+          <t>ARI:0001033</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune hemolytic anemia</t>
+          <t>Autoimmune hepatitis</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>413603009</t>
+          <t>408335007</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune hemolytic anemia</t>
+          <t>Autoimmune hepatitis</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -2064,13 +2040,13 @@
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>441269</t>
+          <t>200762</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>413603009, 718716008</t>
+          <t>721711009, 408335007, 16098491000119109, 721713007, 721712002</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
@@ -2082,22 +2058,22 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001033</t>
+          <t>ARI:0001034</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune hepatitis</t>
+          <t>Autoimmune hypoparathyroidism</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>408335007</t>
+          <t>75316000</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune hepatitis</t>
+          <t>Autoimmune hypoparathyroidism</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -2117,13 +2093,13 @@
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>200762</t>
+          <t>4326738</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr"/>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>408335007, 721711009, 721712002, 721713007, 16098491000119109</t>
+          <t>75316000</t>
         </is>
       </c>
       <c r="K34" s="5" t="inlineStr">
@@ -2135,22 +2111,22 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001034</t>
+          <t>ARI:0001035</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune hypoparathyroidism</t>
+          <t>Autoimmune hypophysitis</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>75316000</t>
+          <t>237706000</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune hypoparathyroidism</t>
+          <t>Autoimmune hypophysitis</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -2170,13 +2146,13 @@
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>4326738</t>
+          <t>4030201</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr"/>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>75316000</t>
+          <t>237706000</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
@@ -2188,100 +2164,100 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001035</t>
+          <t>ARI:0001036</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune hypophysitis</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>237706000</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>Autoimmune hypophysitis</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>0.778</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
+          <t>Autoimmune-Inflammatory Syndrome Induced by Adjuvants</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr"/>
+      <c r="D36" s="3" t="inlineStr"/>
+      <c r="E36" s="2" t="inlineStr"/>
+      <c r="F36" s="2" t="inlineStr"/>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>(preferred name)</t>
-        </is>
-      </c>
-      <c r="H36" s="4" t="inlineStr">
-        <is>
-          <t>4030201</t>
-        </is>
-      </c>
+          <t>no match</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr"/>
       <c r="I36" s="2" t="inlineStr"/>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>237706000</t>
-        </is>
-      </c>
-      <c r="K36" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="J36" s="3" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001036</t>
+          <t>ARI:0001037</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune-Inflammatory Syndrome Induced by Adjuvants</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr"/>
-      <c r="D37" s="3" t="inlineStr"/>
-      <c r="E37" s="2" t="inlineStr"/>
-      <c r="F37" s="2" t="inlineStr"/>
+          <t>Autoimmune limbic encephalitis</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>1300193002</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>Autoimmune limbic encephalitis</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>0.778</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>no match</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr"/>
+          <t>(preferred name)</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>1245375</t>
+        </is>
+      </c>
       <c r="I37" s="2" t="inlineStr"/>
-      <c r="J37" s="3" t="inlineStr"/>
-      <c r="K37" s="2" t="inlineStr"/>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>1300193002</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001037</t>
+          <t>ARI:0001038</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune limbic encephalitis</t>
+          <t>Autoimmune lymphoproliferative syndrome</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>1300193002</t>
+          <t>702444009</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune limbic encephalitis</t>
+          <t>Autoimmune lymphoproliferative syndrome</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -2301,13 +2277,13 @@
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>1245375</t>
+          <t>45765493</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>1300193002</t>
+          <t>702444009</t>
         </is>
       </c>
       <c r="K38" s="5" t="inlineStr">
@@ -2319,22 +2295,22 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001038</t>
+          <t>ARI:0001039</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune lymphoproliferative syndrome</t>
+          <t>Autoimmune necrotizing myopathy</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>702444009</t>
+          <t>715863001</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune lymphoproliferative syndrome</t>
+          <t>Autoimmune necrotizing myopathy</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -2354,13 +2330,13 @@
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>45765493</t>
+          <t>37396156</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>702444009</t>
+          <t>715863001</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
@@ -2372,22 +2348,22 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001039</t>
+          <t>ARI:0001040</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune necrotizing myopathy</t>
+          <t>Autoimmune neutropenia</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>715863001</t>
+          <t>234425008</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune necrotizing myopathy</t>
+          <t>Autoimmune neutropenia</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -2407,13 +2383,13 @@
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>37396156</t>
+          <t>4125635</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>715863001</t>
+          <t>234425008</t>
         </is>
       </c>
       <c r="K40" s="5" t="inlineStr">
@@ -2425,22 +2401,22 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001040</t>
+          <t>ARI:0001041</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune neutropenia</t>
+          <t>Autoimmune oophoritis</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>234425008</t>
+          <t>721198006</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune neutropenia</t>
+          <t>Premature ovarian failure due to autoimmune oophoritis</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -2455,18 +2431,18 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>(preferred name)</t>
+          <t>Premature ovarian failure due to autoimmune oophoritis</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>4125635</t>
+          <t>36717453</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>234425008</t>
+          <t>721198006</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
@@ -2478,22 +2454,22 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001041</t>
+          <t>ARI:0001042</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune oophoritis</t>
+          <t>Autoimmune optic neuropathy</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>721198006</t>
+          <t>838324008</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>Premature ovarian failure due to autoimmune oophoritis</t>
+          <t>Autoimmune optic neuropathy</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -2508,18 +2484,18 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>Premature ovarian failure due to autoimmune oophoritis</t>
+          <t>(preferred name)</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>36717453</t>
+          <t>3654632</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr"/>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>721198006</t>
+          <t>838324008</t>
         </is>
       </c>
       <c r="K42" s="5" t="inlineStr">
@@ -2531,22 +2507,22 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001042</t>
+          <t>ARI:0001043</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune optic neuropathy</t>
+          <t>Autoimmune pancreatitis</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>838324008</t>
+          <t>448542008</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune optic neuropathy</t>
+          <t>Autoimmune pancreatitis</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -2566,13 +2542,13 @@
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>3654632</t>
+          <t>40490446</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr"/>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>838324008</t>
+          <t>722872000, 1197740007, 448542008</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
@@ -2584,22 +2560,22 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001043</t>
+          <t>ARI:0001044</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune pancreatitis</t>
+          <t>Autoimmune progesterone dermatitis</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>448542008</t>
+          <t>838551007</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune pancreatitis</t>
+          <t>Autoimmune progesterone dermatitis</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -2619,13 +2595,13 @@
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>40490446</t>
+          <t>3661498</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr"/>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>448542008, 722872000, 1197740007</t>
+          <t>838551007</t>
         </is>
       </c>
       <c r="K44" s="5" t="inlineStr">
@@ -2637,22 +2613,22 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001044</t>
+          <t>ARI:0001045</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune progesterone dermatitis</t>
+          <t>Autoimmune pulmonary alveolar proteinosis</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>838551007</t>
+          <t>707443007</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune progesterone dermatitis</t>
+          <t>Autoimmune pulmonary alveolar proteinosis</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -2672,13 +2648,13 @@
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>3661498</t>
+          <t>45768909</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr"/>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>838551007</t>
+          <t>707443007</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr">
@@ -2690,100 +2666,100 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001045</t>
+          <t>ARI:0001046</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune pulmonary alveolar proteinosis</t>
-        </is>
-      </c>
-      <c r="C46" s="4" t="inlineStr">
-        <is>
-          <t>707443007</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="inlineStr">
-        <is>
-          <t>Autoimmune pulmonary alveolar proteinosis</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>0.778</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
+          <t>Autoimmune retinal vasculitis</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr"/>
+      <c r="D46" s="3" t="inlineStr"/>
+      <c r="E46" s="2" t="inlineStr"/>
+      <c r="F46" s="2" t="inlineStr"/>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>(preferred name)</t>
-        </is>
-      </c>
-      <c r="H46" s="4" t="inlineStr">
-        <is>
-          <t>45768909</t>
-        </is>
-      </c>
+          <t>no match</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr"/>
       <c r="I46" s="2" t="inlineStr"/>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>707443007</t>
-        </is>
-      </c>
-      <c r="K46" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="J46" s="3" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001046</t>
+          <t>ARI:0001047</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune retinal vasculitis</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr"/>
-      <c r="D47" s="3" t="inlineStr"/>
-      <c r="E47" s="2" t="inlineStr"/>
-      <c r="F47" s="2" t="inlineStr"/>
+          <t>Autoimmune retinopathy</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>724809006</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>Autoimmune retinopathy</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>0.778</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>no match</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr"/>
+          <t>(preferred name)</t>
+        </is>
+      </c>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>37110540</t>
+        </is>
+      </c>
       <c r="I47" s="2" t="inlineStr"/>
-      <c r="J47" s="3" t="inlineStr"/>
-      <c r="K47" s="2" t="inlineStr"/>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>724809006</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001047</t>
+          <t>ARI:0001048</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune retinopathy</t>
+          <t>Autoimmune thyroiditis</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>724809006</t>
+          <t>66944004</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune retinopathy</t>
+          <t>Autoimmune thyroiditis</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -2803,13 +2779,13 @@
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>37110540</t>
+          <t>4281109</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr"/>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>724809006</t>
+          <t>66944004</t>
         </is>
       </c>
       <c r="K48" s="5" t="inlineStr">
@@ -2821,22 +2797,22 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001048</t>
+          <t>ARI:0001049</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune thyroiditis</t>
+          <t>Autoimmune urticaria</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>66944004</t>
+          <t>402397006</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune thyroiditis</t>
+          <t>Autoimmune urticaria</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -2856,13 +2832,13 @@
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>4281109</t>
+          <t>4224623</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr"/>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>66944004, 21983002</t>
+          <t>402397006</t>
         </is>
       </c>
       <c r="K49" s="5" t="inlineStr">
@@ -2874,22 +2850,22 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001049</t>
+          <t>ARI:0001050</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune urticaria</t>
+          <t>Autoimmune urticaria and/or angioedema</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>402397006</t>
+          <t>402402005</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune urticaria</t>
+          <t>Autoimmune urticaria and/or angioedema</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -2909,13 +2885,13 @@
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>4224623</t>
+          <t>4221673</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr"/>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>402397006</t>
+          <t>402402005</t>
         </is>
       </c>
       <c r="K50" s="5" t="inlineStr">
@@ -2927,22 +2903,22 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001050</t>
+          <t>ARI:0001051</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune urticaria and/or angioedema</t>
+          <t>Autoimmune vasculitis</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>402402005</t>
+          <t>427213005</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune urticaria and/or angioedema</t>
+          <t>Autoimmune vasculitis</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -2962,13 +2938,13 @@
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>4221673</t>
+          <t>4146124</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr"/>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>402402005</t>
+          <t>427213005</t>
         </is>
       </c>
       <c r="K51" s="5" t="inlineStr">
@@ -2980,22 +2956,22 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001051</t>
+          <t>ARI:0001052</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune vasculitis</t>
+          <t>Balo concentric sclerosis</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>427213005</t>
+          <t>230380005</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune vasculitis</t>
+          <t>Balo concentric sclerosis</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -3015,13 +2991,13 @@
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>4146124</t>
+          <t>4046110</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr"/>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>427213005</t>
+          <t>230380005</t>
         </is>
       </c>
       <c r="K52" s="5" t="inlineStr">
@@ -3033,22 +3009,22 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001052</t>
+          <t>ARI:0001053</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>Balo concentric sclerosis</t>
+          <t>Behçet's syndrome</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>230380005</t>
+          <t>310701003</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>Balo concentric sclerosis</t>
+          <t>Behcet's syndrome</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -3063,18 +3039,18 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>(preferred name)</t>
+          <t>Behcet's syndrome</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>4046110</t>
+          <t>436642</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr"/>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>230380005</t>
+          <t>310701003</t>
         </is>
       </c>
       <c r="K53" s="5" t="inlineStr">
@@ -3086,22 +3062,22 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001053</t>
+          <t>ARI:0001054</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Behçet's syndrome</t>
+          <t>Benign mucous membrane pemphigoid</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>310701003</t>
+          <t>34250006</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>Behcet's syndrome</t>
+          <t>Benign mucous membrane pemphigoid</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -3116,18 +3092,18 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>Behcet's syndrome</t>
+          <t>(preferred name)</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>436642</t>
+          <t>4142060</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr"/>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>310701003, 721226005</t>
+          <t>34250006</t>
         </is>
       </c>
       <c r="K54" s="5" t="inlineStr">
@@ -3139,22 +3115,22 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001054</t>
+          <t>ARI:0001055</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>Benign mucous membrane pemphigoid</t>
+          <t>Bickerstaff's brainstem encephalitis</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>34250006</t>
+          <t>427086003</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>Benign mucous membrane pemphigoid</t>
+          <t>Bickerstaff's brainstem encephalitis</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -3174,13 +3150,13 @@
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>4142060</t>
+          <t>4141686</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr"/>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>34250006, 314757003</t>
+          <t>427086003</t>
         </is>
       </c>
       <c r="K55" s="5" t="inlineStr">
@@ -3192,22 +3168,22 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001055</t>
+          <t>ARI:0001056</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Bickerstaff's brainstem encephalitis</t>
+          <t>Birdshot chorioretinopathy</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>427086003</t>
+          <t>231981005</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>Bickerstaff's brainstem encephalitis</t>
+          <t>Birdshot chorioretinitis</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -3222,18 +3198,18 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>(preferred name)</t>
+          <t>Birdshot chorioretinitis</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>4141686</t>
+          <t>4334133</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr"/>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>427086003</t>
+          <t>231981005</t>
         </is>
       </c>
       <c r="K56" s="5" t="inlineStr">
@@ -3245,22 +3221,22 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001056</t>
+          <t>ARI:0001057</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>Birdshot chorioretinopathy</t>
+          <t>Bullous pemphigoid</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>231981005</t>
+          <t>77090002</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>Birdshot chorioretinitis</t>
+          <t>Bullous pemphigoid</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -3275,18 +3251,18 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>Birdshot chorioretinitis</t>
+          <t>(preferred name)</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>4334133</t>
+          <t>4298692</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr"/>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>231981005</t>
+          <t>77090002</t>
         </is>
       </c>
       <c r="K57" s="5" t="inlineStr">
@@ -3298,22 +3274,22 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001057</t>
+          <t>ARI:0001058</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Bullous pemphigoid</t>
+          <t>Bullous systemic lupus erythematosus</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>77090002</t>
+          <t>239889005</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>Bullous pemphigoid</t>
+          <t>Bullous systemic lupus erythematosus</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -3333,13 +3309,13 @@
       </c>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>4298692</t>
+          <t>4346976</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr"/>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>77090002</t>
+          <t>239889005</t>
         </is>
       </c>
       <c r="K58" s="5" t="inlineStr">
@@ -3351,22 +3327,22 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001058</t>
+          <t>ARI:0001059</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>Bullous systemic lupus erythematosus</t>
+          <t>Calcinosis due to childhood type dermatomyositis</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>239889005</t>
+          <t>838312001</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>Bullous systemic lupus erythematosus</t>
+          <t>Calcinosis due to childhood type dermatomyositis</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -3386,13 +3362,13 @@
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>4346976</t>
+          <t>3654620</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr"/>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>239889005</t>
+          <t>838312001</t>
         </is>
       </c>
       <c r="K59" s="5" t="inlineStr">
@@ -3404,22 +3380,22 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001059</t>
+          <t>ARI:0001060</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Calcinosis due to childhood type dermatomyositis</t>
+          <t>Cataplexy and narcolepsy</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>838312001</t>
+          <t>193042000</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>Calcinosis due to childhood type dermatomyositis</t>
+          <t>Cataplexy and narcolepsy</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -3439,13 +3415,13 @@
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>3654620</t>
+          <t>437854</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr"/>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>838312001</t>
+          <t>193042000</t>
         </is>
       </c>
       <c r="K60" s="5" t="inlineStr">
@@ -3457,22 +3433,22 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001060</t>
+          <t>ARI:0001061</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>Cataplexy and narcolepsy</t>
+          <t>Celiac disease</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>193042000</t>
+          <t>396331005</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>Cataplexy and narcolepsy</t>
+          <t>Celiac disease</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -3492,13 +3468,13 @@
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>437854</t>
+          <t>194992</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr"/>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>193042000, 735676003</t>
+          <t>396331005</t>
         </is>
       </c>
       <c r="K61" s="5" t="inlineStr">
@@ -3510,22 +3486,22 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001061</t>
+          <t>ARI:0001062</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Celiac disease</t>
+          <t>Chronic Fatigue Syndrome</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>396331005</t>
+          <t>51771007</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>Celiac disease</t>
+          <t>Postviral fatigue syndrome</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -3540,50 +3516,46 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>(preferred name)</t>
+          <t>Postviral fatigue syndrome</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr">
         <is>
-          <t>194992</t>
+          <t>4202045</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr"/>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>91867008, 396331005</t>
-        </is>
-      </c>
-      <c r="K62" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>52702003</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001062</t>
+          <t>ARI:0001063</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>Chronic Fatigue Syndrome</t>
+          <t>Chronic inflammatory demyelinating polyradiculoneuropathy</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>52702003</t>
+          <t>128209004</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>Chronic fatigue syndrome</t>
+          <t>Chronic inflammatory demyelinating polyradiculoneuropathy</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>0.772</t>
+          <t>0.778</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -3598,13 +3570,13 @@
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>432738</t>
+          <t>381009</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr"/>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>52702003</t>
+          <t>128209004</t>
         </is>
       </c>
       <c r="K63" s="5" t="inlineStr">
@@ -3616,32 +3588,32 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001063</t>
+          <t>ARI:0001064</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>Chronic inflammatory demyelinating polyradiculoneuropathy</t>
+          <t>Chronic interstitial cystitis</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>128209004</t>
+          <t>38731000087104</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>Chronic inflammatory demyelinating polyradiculoneuropathy</t>
+          <t>Chronic primary bladder pain syndrome</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>0.778</t>
+          <t>0.556</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>synonym</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
@@ -3651,13 +3623,13 @@
       </c>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t>381009</t>
+          <t>1450471</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr"/>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>128209004, 230564004</t>
+          <t>38731000087104</t>
         </is>
       </c>
       <c r="K64" s="5" t="inlineStr">
@@ -3669,76 +3641,52 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001064</t>
+          <t>ARI:0001065</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>Chronic interstitial cystitis</t>
-        </is>
-      </c>
-      <c r="C65" s="4" t="inlineStr">
-        <is>
-          <t>38731000087104</t>
-        </is>
-      </c>
-      <c r="D65" s="3" t="inlineStr">
-        <is>
-          <t>Chronic primary bladder pain syndrome</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>0.556</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="inlineStr">
-        <is>
-          <t>synonym</t>
-        </is>
-      </c>
+          <t>Chronic Lyme disease</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr"/>
+      <c r="D65" s="3" t="inlineStr"/>
+      <c r="E65" s="2" t="inlineStr"/>
+      <c r="F65" s="2" t="inlineStr"/>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>(preferred name)</t>
-        </is>
-      </c>
-      <c r="H65" s="4" t="inlineStr">
-        <is>
-          <t>1450471</t>
-        </is>
-      </c>
+          <t>no match</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr"/>
       <c r="I65" s="2" t="inlineStr"/>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>197834003</t>
-        </is>
-      </c>
+      <c r="J65" s="3" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001065</t>
+          <t>ARI:0001066</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>Chronic Lyme disease</t>
+          <t>Chronic multifocal osteomyelitis</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>23502006</t>
+          <t>1204420006</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>Lyme disease</t>
+          <t>Chronic nonbacterial osteomyelitis/chronic recurrent multifocal osteomyelitis</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>0.778</t>
+          <t>0.734</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -3748,18 +3696,18 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>Lyme disease</t>
+          <t>Chronic nonbacterial osteomyelitis/Chronic recurrent multifocal osteomyelitis</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>440638</t>
+          <t>37163124</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr"/>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>33937009, 23502006</t>
+          <t>1204420006</t>
         </is>
       </c>
       <c r="K66" s="5" t="inlineStr">
@@ -3771,12 +3719,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001066</t>
+          <t>ARI:0001067</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>Chronic multifocal osteomyelitis</t>
+          <t>Chronic post-COVID-19 syndrome</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr"/>
@@ -3792,7 +3740,7 @@
       <c r="I67" s="2" t="inlineStr"/>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>240151005</t>
+          <t>1119304009</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr"/>
@@ -3800,56 +3748,80 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001067</t>
+          <t>ARI:0001068</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>Chronic post-COVID-19 syndrome</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr"/>
-      <c r="D68" s="3" t="inlineStr"/>
-      <c r="E68" s="2" t="inlineStr"/>
-      <c r="F68" s="2" t="inlineStr"/>
+          <t>Cogan's syndrome</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>405810005</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>Cogan's syndrome</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>0.778</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>no match</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="inlineStr"/>
+          <t>(preferred name)</t>
+        </is>
+      </c>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>4233620</t>
+        </is>
+      </c>
       <c r="I68" s="2" t="inlineStr"/>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>1119304009</t>
-        </is>
-      </c>
-      <c r="K68" s="2" t="inlineStr"/>
+          <t>405810005</t>
+        </is>
+      </c>
+      <c r="K68" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001068</t>
+          <t>ARI:0001069</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>Cogan's syndrome</t>
+          <t>Cold agglutinin disease</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>405810005</t>
+          <t>127055007</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>Cogan's syndrome</t>
+          <t>Chronic cold agglutinin disease</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>0.778</t>
+          <t>0.772</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -3859,45 +3831,41 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>(preferred name)</t>
+          <t>chronic cold agglutinin disease</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>4233620</t>
+          <t>4131128</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr"/>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>405810005</t>
-        </is>
-      </c>
-      <c r="K69" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>398937006</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001069</t>
+          <t>ARI:0001070</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>Cold agglutinin disease</t>
+          <t>Combined immunodeficiency due to LRBA deficiency</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>398937006</t>
+          <t>1197477000</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>Cold autoimmune hemolytic anemia</t>
+          <t>Combined immunodeficiency due to LRBA deficiency</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -3912,18 +3880,18 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>Cold autoimmune hemolytic anemia</t>
+          <t>(preferred name)</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>4160887</t>
+          <t>37162777</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr"/>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>398937006, 127055007</t>
+          <t>1197477000</t>
         </is>
       </c>
       <c r="K70" s="5" t="inlineStr">
@@ -3935,22 +3903,22 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001070</t>
+          <t>ARI:0001071</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>Combined immunodeficiency due to LRBA deficiency</t>
+          <t>Complex regional pain syndrome</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>1197477000</t>
+          <t>128200000</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>Combined immunodeficiency due to LRBA deficiency</t>
+          <t>Complex regional pain syndrome</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -3970,13 +3938,13 @@
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>37162777</t>
+          <t>4134577</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr"/>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>1197477000</t>
+          <t>128200000</t>
         </is>
       </c>
       <c r="K71" s="5" t="inlineStr">
@@ -3988,100 +3956,104 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001071</t>
+          <t>ARI:0001072</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>Complex regional pain syndrome</t>
-        </is>
-      </c>
-      <c r="C72" s="4" t="inlineStr">
-        <is>
-          <t>128200000</t>
-        </is>
-      </c>
-      <c r="D72" s="3" t="inlineStr">
-        <is>
-          <t>Complex regional pain syndrome</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>0.778</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
+          <t>COPA syndrome</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr"/>
+      <c r="D72" s="3" t="inlineStr"/>
+      <c r="E72" s="2" t="inlineStr"/>
+      <c r="F72" s="2" t="inlineStr"/>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>(preferred name)</t>
-        </is>
-      </c>
-      <c r="H72" s="4" t="inlineStr">
-        <is>
-          <t>4134577</t>
-        </is>
-      </c>
+          <t>no match</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr"/>
       <c r="I72" s="2" t="inlineStr"/>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>128200000, 408751001, 734947007</t>
-        </is>
-      </c>
-      <c r="K72" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>1222679006</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001072</t>
+          <t>ARI:0001073</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>COPA syndrome</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr"/>
-      <c r="D73" s="3" t="inlineStr"/>
-      <c r="E73" s="2" t="inlineStr"/>
-      <c r="F73" s="2" t="inlineStr"/>
+          <t>Crohn's disease</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>34000006</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>Crohn's disease</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>0.778</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>no match</t>
-        </is>
-      </c>
-      <c r="H73" s="2" t="inlineStr"/>
+          <t>(preferred name)</t>
+        </is>
+      </c>
+      <c r="H73" s="4" t="inlineStr">
+        <is>
+          <t>201606</t>
+        </is>
+      </c>
       <c r="I73" s="2" t="inlineStr"/>
-      <c r="J73" s="3" t="inlineStr"/>
-      <c r="K73" s="2" t="inlineStr"/>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>34000006</t>
+        </is>
+      </c>
+      <c r="K73" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001073</t>
+          <t>ARI:0001074</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>Crohn's disease</t>
+          <t>Cryptogenic organizing pneumonia</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>34000006</t>
+          <t>719218000</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>Crohn's disease</t>
+          <t>Cryptogenic organizing pneumonia</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -4101,13 +4073,13 @@
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>201606</t>
+          <t>36714118</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr"/>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>34000006</t>
+          <t>719218000</t>
         </is>
       </c>
       <c r="K74" s="5" t="inlineStr">
@@ -4119,100 +4091,100 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001074</t>
+          <t>ARI:0001075</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>Cryptogenic organizing pneumonia</t>
-        </is>
-      </c>
-      <c r="C75" s="4" t="inlineStr">
-        <is>
-          <t>719218000</t>
-        </is>
-      </c>
-      <c r="D75" s="3" t="inlineStr">
-        <is>
-          <t>Cryptogenic organizing pneumonia</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>0.778</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
+          <t>CTLA4 haploinsufficiency</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr"/>
+      <c r="D75" s="3" t="inlineStr"/>
+      <c r="E75" s="2" t="inlineStr"/>
+      <c r="F75" s="2" t="inlineStr"/>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>(preferred name)</t>
-        </is>
-      </c>
-      <c r="H75" s="4" t="inlineStr">
-        <is>
-          <t>36714118</t>
-        </is>
-      </c>
+          <t>no match</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr"/>
       <c r="I75" s="2" t="inlineStr"/>
-      <c r="J75" s="3" t="inlineStr">
-        <is>
-          <t>719218000</t>
-        </is>
-      </c>
-      <c r="K75" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="J75" s="3" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001075</t>
+          <t>ARI:0001076</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>CTLA4 haploinsufficiency</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr"/>
-      <c r="D76" s="3" t="inlineStr"/>
-      <c r="E76" s="2" t="inlineStr"/>
-      <c r="F76" s="2" t="inlineStr"/>
+          <t>Cutaneous lupus erythematosus</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>7119001</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>Cutaneous lupus erythematosus</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>0.778</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>no match</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr"/>
+          <t>(preferred name)</t>
+        </is>
+      </c>
+      <c r="H76" s="4" t="inlineStr">
+        <is>
+          <t>4324123</t>
+        </is>
+      </c>
       <c r="I76" s="2" t="inlineStr"/>
-      <c r="J76" s="3" t="inlineStr"/>
-      <c r="K76" s="2" t="inlineStr"/>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>7119001</t>
+        </is>
+      </c>
+      <c r="K76" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001076</t>
+          <t>ARI:0001077</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>Cutaneous lupus erythematosus</t>
+          <t>Cutaneous mastocytosis</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>7119001</t>
+          <t>397012002</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>Cutaneous lupus erythematosus</t>
+          <t>Cutaneous mastocytosis</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -4232,13 +4204,13 @@
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t>4324123</t>
+          <t>4246283</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr"/>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>238927000, 7119001, 200938002, 403495008, 200941006, 239891002</t>
+          <t>397012002</t>
         </is>
       </c>
       <c r="K77" s="5" t="inlineStr">
@@ -4250,22 +4222,22 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001077</t>
+          <t>ARI:0001078</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>Cutaneous mastocytosis</t>
+          <t>Dermatitis herpetiformis</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>397012002</t>
+          <t>111196000</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>Cutaneous mastocytosis</t>
+          <t>Dermatitis herpetiformis</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -4285,13 +4257,13 @@
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
-          <t>4246283</t>
+          <t>140487</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr"/>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>397012002</t>
+          <t>111196000</t>
         </is>
       </c>
       <c r="K78" s="5" t="inlineStr">
@@ -4303,22 +4275,22 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001078</t>
+          <t>ARI:0001079</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>Dermatitis herpetiformis</t>
+          <t>Dermatomyositis</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>111196000</t>
+          <t>396230008</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>Dermatitis herpetiformis</t>
+          <t>Dermatomyositis</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -4338,13 +4310,13 @@
       </c>
       <c r="H79" s="4" t="inlineStr">
         <is>
-          <t>140487</t>
+          <t>80182</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr"/>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>111196000</t>
+          <t>396230008, 1212005</t>
         </is>
       </c>
       <c r="K79" s="5" t="inlineStr">
@@ -4356,22 +4328,22 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001079</t>
+          <t>ARI:0001080</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>Dermatomyositis</t>
+          <t>Type 1 diabetes mellitus</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>396230008</t>
+          <t>46635009</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>Dermatomyositis</t>
+          <t>Type 1 diabetes mellitus</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -4391,13 +4363,13 @@
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
-          <t>80182</t>
+          <t>201254</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr"/>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>396230008, 1212005</t>
+          <t>46635009</t>
         </is>
       </c>
       <c r="K80" s="5" t="inlineStr">
@@ -4409,22 +4381,22 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001080</t>
+          <t>ARI:0001081</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>Diabetes mellitus type 1</t>
+          <t>Eaton-Lambert syndrome</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>46635009</t>
+          <t>56989000</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>Type 1 diabetes mellitus</t>
+          <t>Eaton-Lambert syndrome</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -4439,18 +4411,18 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>Type 1 diabetes mellitus</t>
+          <t>(preferred name)</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
-          <t>201254</t>
+          <t>4237155</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr"/>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>46635009</t>
+          <t>56989000</t>
         </is>
       </c>
       <c r="K81" s="5" t="inlineStr">
@@ -4462,65 +4434,37 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001081</t>
+          <t>ARI:0001082</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>Eaton-Lambert syndrome</t>
-        </is>
-      </c>
-      <c r="C82" s="4" t="inlineStr">
-        <is>
-          <t>56989000</t>
-        </is>
-      </c>
-      <c r="D82" s="3" t="inlineStr">
-        <is>
-          <t>Eaton-Lambert syndrome</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>0.778</t>
-        </is>
-      </c>
-      <c r="F82" s="2" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
+          <t>Encephalitis caused by anti-gamma-aminobutyric acid-A receptor antibody</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr"/>
+      <c r="D82" s="3" t="inlineStr"/>
+      <c r="E82" s="2" t="inlineStr"/>
+      <c r="F82" s="2" t="inlineStr"/>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>(preferred name)</t>
-        </is>
-      </c>
-      <c r="H82" s="4" t="inlineStr">
-        <is>
-          <t>4237155</t>
-        </is>
-      </c>
+          <t>no match</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr"/>
       <c r="I82" s="2" t="inlineStr"/>
-      <c r="J82" s="3" t="inlineStr">
-        <is>
-          <t>56989000</t>
-        </is>
-      </c>
-      <c r="K82" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="J82" s="3" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001082</t>
+          <t>ARI:0001083</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>Encephalitis caused by anti-gamma-aminobutyric acid-A receptor antibody</t>
+          <t>Encephalopathy caused by anti-IgLON5 antibody</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr"/>
@@ -4540,57 +4484,85 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001083</t>
+          <t>ARI:0001084</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>Encephalopathy caused by anti-IgLON5 antibody</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr"/>
-      <c r="D84" s="3" t="inlineStr"/>
-      <c r="E84" s="2" t="inlineStr"/>
-      <c r="F84" s="2" t="inlineStr"/>
+          <t>Endometriosis</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr">
+        <is>
+          <t>129103003</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>Endometriosis (clinical)</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>0.556</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>synonym</t>
+        </is>
+      </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>no match</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr"/>
+          <t>(preferred name)</t>
+        </is>
+      </c>
+      <c r="H84" s="4" t="inlineStr">
+        <is>
+          <t>433527</t>
+        </is>
+      </c>
       <c r="I84" s="2" t="inlineStr"/>
-      <c r="J84" s="3" t="inlineStr"/>
-      <c r="K84" s="2" t="inlineStr"/>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>129103003</t>
+        </is>
+      </c>
+      <c r="K84" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001084</t>
+          <t>ARI:0001085</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>Endometriosis</t>
+          <t>Enthesitis</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>129103003</t>
+          <t>359643005</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>Endometriosis (clinical)</t>
+          <t>Enthesitis</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>0.556</t>
+          <t>0.778</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>synonym</t>
+          <t>name</t>
         </is>
       </c>
       <c r="G85" s="3" t="inlineStr">
@@ -4600,13 +4572,13 @@
       </c>
       <c r="H85" s="4" t="inlineStr">
         <is>
-          <t>433527</t>
+          <t>4231746</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr"/>
       <c r="J85" s="3" t="inlineStr">
         <is>
-          <t>129103003</t>
+          <t>359643005</t>
         </is>
       </c>
       <c r="K85" s="5" t="inlineStr">
@@ -4618,22 +4590,22 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001085</t>
+          <t>ARI:0001086</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>Enthesitis</t>
+          <t>Eosinophilic esophagitis</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>359643005</t>
+          <t>235599003</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>Enthesitis</t>
+          <t>Eosinophilic esophagitis</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -4653,13 +4625,13 @@
       </c>
       <c r="H86" s="4" t="inlineStr">
         <is>
-          <t>4231746</t>
+          <t>27918</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr"/>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>359643005</t>
+          <t>235599003</t>
         </is>
       </c>
       <c r="K86" s="5" t="inlineStr">
@@ -4671,22 +4643,22 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001086</t>
+          <t>ARI:0001087</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>Eosinophilic esophagitis</t>
+          <t>Epilepsy</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>235599003</t>
+          <t>84757009</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>Eosinophilic esophagitis</t>
+          <t>Epilepsy</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -4706,13 +4678,13 @@
       </c>
       <c r="H87" s="4" t="inlineStr">
         <is>
-          <t>27918</t>
+          <t>380378</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr"/>
       <c r="J87" s="3" t="inlineStr">
         <is>
-          <t>235599003</t>
+          <t>84757009</t>
         </is>
       </c>
       <c r="K87" s="5" t="inlineStr">
@@ -4724,22 +4696,22 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001087</t>
+          <t>ARI:0001088</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>Epilepsy</t>
+          <t>Episcleritis</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>84757009</t>
+          <t>815008</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>Epilepsy</t>
+          <t>Episcleritis</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -4759,13 +4731,13 @@
       </c>
       <c r="H88" s="4" t="inlineStr">
         <is>
-          <t>380378</t>
+          <t>4218083</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr"/>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>84757009</t>
+          <t>815008</t>
         </is>
       </c>
       <c r="K88" s="5" t="inlineStr">
@@ -4777,22 +4749,22 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001088</t>
+          <t>ARI:0001089</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>Episcleritis</t>
+          <t>Erythema nodosum</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>815008</t>
+          <t>32861005</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>Episcleritis</t>
+          <t>Erythema nodosum</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -4812,13 +4784,13 @@
       </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
-          <t>4218083</t>
+          <t>140176</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr"/>
       <c r="J89" s="3" t="inlineStr">
         <is>
-          <t>815008</t>
+          <t>32861005</t>
         </is>
       </c>
       <c r="K89" s="5" t="inlineStr">
@@ -4830,22 +4802,22 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001089</t>
+          <t>ARI:0001090</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>Erythema nodosum</t>
+          <t>Essential mixed cryoglobulinemia</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>32861005</t>
+          <t>239947001</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>Erythema nodosum</t>
+          <t>Essential mixed cryoglobulinemia</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -4865,13 +4837,13 @@
       </c>
       <c r="H90" s="4" t="inlineStr">
         <is>
-          <t>140176</t>
+          <t>4347067</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr"/>
       <c r="J90" s="3" t="inlineStr">
         <is>
-          <t>32861005</t>
+          <t>239947001</t>
         </is>
       </c>
       <c r="K90" s="5" t="inlineStr">
@@ -4883,22 +4855,22 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001090</t>
+          <t>ARI:0001091</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>Essential mixed cryoglobulinemia</t>
+          <t>Evans syndrome</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>239947001</t>
+          <t>75331009</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>Essential mixed cryoglobulinemia</t>
+          <t>Evans syndrome</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -4918,13 +4890,13 @@
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>4347067</t>
+          <t>436956</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr"/>
       <c r="J91" s="3" t="inlineStr">
         <is>
-          <t>239947001</t>
+          <t>75331009</t>
         </is>
       </c>
       <c r="K91" s="5" t="inlineStr">
@@ -4936,22 +4908,22 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001091</t>
+          <t>ARI:0001092</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>Evans syndrome</t>
+          <t>Fasciitis with eosinophilia syndrome</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>75331009</t>
+          <t>24129002</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>Evans syndrome</t>
+          <t>Fasciitis with eosinophilia syndrome</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -4971,13 +4943,13 @@
       </c>
       <c r="H92" s="4" t="inlineStr">
         <is>
-          <t>436956</t>
+          <t>4083100</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr"/>
       <c r="J92" s="3" t="inlineStr">
         <is>
-          <t>75331009</t>
+          <t>24129002</t>
         </is>
       </c>
       <c r="K92" s="5" t="inlineStr">
@@ -4989,22 +4961,22 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001092</t>
+          <t>ARI:0001093</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>Fasciitis with eosinophilia syndrome</t>
+          <t>Felty syndrome</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>24129002</t>
+          <t>57160007</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>Fasciitis with eosinophilia syndrome</t>
+          <t>Felty's syndrome</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -5019,18 +4991,18 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>(preferred name)</t>
+          <t>Felty's syndrome</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
-          <t>4083100</t>
+          <t>81097</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr"/>
       <c r="J93" s="3" t="inlineStr">
         <is>
-          <t>24129002</t>
+          <t>57160007</t>
         </is>
       </c>
       <c r="K93" s="5" t="inlineStr">
@@ -5042,27 +5014,27 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001093</t>
+          <t>ARI:0001094</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>Felty syndrome</t>
+          <t>Female infertility due to antisperm antibodies</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>57160007</t>
+          <t>414238007</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>Felty's syndrome</t>
+          <t>Female infertility due to antisperm antibody</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>0.778</t>
+          <t>0.772</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
@@ -5072,18 +5044,18 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>Felty's syndrome</t>
+          <t>(preferred name)</t>
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr">
         <is>
-          <t>81097</t>
+          <t>4188008</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr"/>
       <c r="J94" s="3" t="inlineStr">
         <is>
-          <t>57160007</t>
+          <t>414238007</t>
         </is>
       </c>
       <c r="K94" s="5" t="inlineStr">
@@ -5095,27 +5067,27 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001094</t>
+          <t>ARI:0001095</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>Female infertility due to antisperm antibodies</t>
+          <t>Fibromyalgia</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>414238007</t>
+          <t>203082005</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>Female infertility due to antisperm antibody</t>
+          <t>Fibromyalgia</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>0.772</t>
+          <t>0.778</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
@@ -5130,13 +5102,13 @@
       </c>
       <c r="H95" s="4" t="inlineStr">
         <is>
-          <t>4188008</t>
+          <t>40405599</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr"/>
       <c r="J95" s="3" t="inlineStr">
         <is>
-          <t>414238007, 236816007</t>
+          <t>203082005</t>
         </is>
       </c>
       <c r="K95" s="5" t="inlineStr">
@@ -5148,22 +5120,22 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001095</t>
+          <t>ARI:0001096</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>Fibromyalgia</t>
+          <t>Graves' disease</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>203082005</t>
+          <t>353295004</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>Fibromyalgia</t>
+          <t>Graves' disease</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -5183,13 +5155,13 @@
       </c>
       <c r="H96" s="4" t="inlineStr">
         <is>
-          <t>40405599</t>
+          <t>4232076</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr"/>
       <c r="J96" s="3" t="inlineStr">
         <is>
-          <t>203082005</t>
+          <t>353295004</t>
         </is>
       </c>
       <c r="K96" s="5" t="inlineStr">
@@ -5201,22 +5173,22 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001096</t>
+          <t>ARI:0001097</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>Graves' disease</t>
+          <t>Guillain-Barré syndrome</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>353295004</t>
+          <t>40956001</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>Graves' disease</t>
+          <t>Guillain-Barré syndrome</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -5236,13 +5208,13 @@
       </c>
       <c r="H97" s="4" t="inlineStr">
         <is>
-          <t>4232076</t>
+          <t>4164770</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr"/>
       <c r="J97" s="3" t="inlineStr">
         <is>
-          <t>353295004, 90739004, 237499004</t>
+          <t>40956001</t>
         </is>
       </c>
       <c r="K97" s="5" t="inlineStr">
@@ -5254,22 +5226,22 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001097</t>
+          <t>ARI:0001098</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>Guillain-Barré syndrome</t>
+          <t>Hemophilia B Leyden</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>40956001</t>
+          <t>1336117005</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>Guillain-Barré syndrome</t>
+          <t>Hemophilia B Leyden</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -5289,13 +5261,13 @@
       </c>
       <c r="H98" s="4" t="inlineStr">
         <is>
-          <t>4164770</t>
+          <t>1076202</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr"/>
       <c r="J98" s="3" t="inlineStr">
         <is>
-          <t>715770009, 1767005, 40956001, 716723000</t>
+          <t>1336117005</t>
         </is>
       </c>
       <c r="K98" s="5" t="inlineStr">
@@ -5307,22 +5279,22 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001098</t>
+          <t>ARI:0001099</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>Hemophilia B Leyden</t>
+          <t>Herpes gestationis</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>1336117005</t>
+          <t>86081009</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>Hemophilia B Leyden</t>
+          <t>Herpes gestationis</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -5342,13 +5314,13 @@
       </c>
       <c r="H99" s="4" t="inlineStr">
         <is>
-          <t>1076202</t>
+          <t>4311256</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr"/>
       <c r="J99" s="3" t="inlineStr">
         <is>
-          <t>1336117005</t>
+          <t>86081009</t>
         </is>
       </c>
       <c r="K99" s="5" t="inlineStr">
@@ -5360,22 +5332,22 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001099</t>
+          <t>ARI:0001100</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>Herpes gestationis</t>
+          <t>Hidradenitis suppurativa</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>86081009</t>
+          <t>59393003</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>Herpes gestationis</t>
+          <t>Hidradenitis suppurativa</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -5395,13 +5367,13 @@
       </c>
       <c r="H100" s="4" t="inlineStr">
         <is>
-          <t>4311256</t>
+          <t>4241223</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr"/>
       <c r="J100" s="3" t="inlineStr">
         <is>
-          <t>86081009</t>
+          <t>59393003</t>
         </is>
       </c>
       <c r="K100" s="5" t="inlineStr">
@@ -5413,22 +5385,22 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001100</t>
+          <t>ARI:0001101</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>Hidradenitis suppurativa</t>
+          <t>Hypersensitivity angiitis</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>59393003</t>
+          <t>60555002</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>Hidradenitis suppurativa</t>
+          <t>Hypersensitivity angiitis</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -5448,13 +5420,13 @@
       </c>
       <c r="H101" s="4" t="inlineStr">
         <is>
-          <t>4241223</t>
+          <t>196431</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr"/>
       <c r="J101" s="3" t="inlineStr">
         <is>
-          <t>59393003</t>
+          <t>60555002</t>
         </is>
       </c>
       <c r="K101" s="5" t="inlineStr">
@@ -5466,22 +5438,22 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001101</t>
+          <t>ARI:0001102</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>Hypersensitivity angiitis</t>
+          <t>Idiopathic membranous glomerulonephritis</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>60555002</t>
+          <t>722119002</t>
         </is>
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>Hypersensitivity angiitis</t>
+          <t>Idiopathic membranous glomerulonephritis</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -5501,13 +5473,13 @@
       </c>
       <c r="H102" s="4" t="inlineStr">
         <is>
-          <t>196431</t>
+          <t>36716199</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr"/>
       <c r="J102" s="3" t="inlineStr">
         <is>
-          <t>60555002</t>
+          <t>722119002</t>
         </is>
       </c>
       <c r="K102" s="5" t="inlineStr">
@@ -5519,22 +5491,22 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001102</t>
+          <t>ARI:0001103</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>Idiopathic membranous glomerulonephritis</t>
+          <t>Idiopathic pulmonary fibrosis</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>722119002</t>
+          <t>700250006</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>Idiopathic membranous glomerulonephritis</t>
+          <t>Idiopathic pulmonary fibrosis</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -5554,13 +5526,13 @@
       </c>
       <c r="H103" s="4" t="inlineStr">
         <is>
-          <t>36716199</t>
+          <t>45763750</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr"/>
       <c r="J103" s="3" t="inlineStr">
         <is>
-          <t>722119002</t>
+          <t>700250006</t>
         </is>
       </c>
       <c r="K103" s="5" t="inlineStr">
@@ -5572,22 +5544,22 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001103</t>
+          <t>ARI:0001104</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>Idiopathic pulmonary fibrosis</t>
+          <t>IgA nephropathy</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>700250006</t>
+          <t>236407003</t>
         </is>
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>Idiopathic pulmonary fibrosis</t>
+          <t>IgA nephropathy</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -5607,13 +5579,13 @@
       </c>
       <c r="H104" s="4" t="inlineStr">
         <is>
-          <t>45763750</t>
+          <t>4128061</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr"/>
       <c r="J104" s="3" t="inlineStr">
         <is>
-          <t>700250006</t>
+          <t>236407003</t>
         </is>
       </c>
       <c r="K104" s="5" t="inlineStr">
@@ -5625,65 +5597,37 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001104</t>
+          <t>ARI:0001105</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>IgA nephropathy</t>
-        </is>
-      </c>
-      <c r="C105" s="4" t="inlineStr">
-        <is>
-          <t>236407003</t>
-        </is>
-      </c>
-      <c r="D105" s="3" t="inlineStr">
-        <is>
-          <t>IgA nephropathy</t>
-        </is>
-      </c>
-      <c r="E105" s="2" t="inlineStr">
-        <is>
-          <t>0.778</t>
-        </is>
-      </c>
-      <c r="F105" s="2" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
+          <t>Immune checkpoint inhibitor-induced autoimmunity</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr"/>
+      <c r="D105" s="3" t="inlineStr"/>
+      <c r="E105" s="2" t="inlineStr"/>
+      <c r="F105" s="2" t="inlineStr"/>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>(preferred name)</t>
-        </is>
-      </c>
-      <c r="H105" s="4" t="inlineStr">
-        <is>
-          <t>4128061</t>
-        </is>
-      </c>
+          <t>no match</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr"/>
       <c r="I105" s="2" t="inlineStr"/>
-      <c r="J105" s="3" t="inlineStr">
-        <is>
-          <t>236407003</t>
-        </is>
-      </c>
-      <c r="K105" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="J105" s="3" t="inlineStr"/>
+      <c r="K105" s="2" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001105</t>
+          <t>ARI:0001106</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>Immune checkpoint inhibitor-induced autoimmunity</t>
+          <t>Immune Dysregulation, Polyendocrinopathy, Enteropathy, X-Linked Syndrome</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr"/>
@@ -5703,47 +5647,75 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001106</t>
+          <t>ARI:0001107</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>Immune Dysregulation, Polyendocrinopathy, Enteropathy, X-Linked Syndrome</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr"/>
-      <c r="D107" s="3" t="inlineStr"/>
-      <c r="E107" s="2" t="inlineStr"/>
-      <c r="F107" s="2" t="inlineStr"/>
+          <t>Immune thrombocytopenia</t>
+        </is>
+      </c>
+      <c r="C107" s="4" t="inlineStr">
+        <is>
+          <t>2897005</t>
+        </is>
+      </c>
+      <c r="D107" s="3" t="inlineStr">
+        <is>
+          <t>Immune thrombocytopenia</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>0.778</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>no match</t>
-        </is>
-      </c>
-      <c r="H107" s="2" t="inlineStr"/>
+          <t>(preferred name)</t>
+        </is>
+      </c>
+      <c r="H107" s="4" t="inlineStr">
+        <is>
+          <t>4103532</t>
+        </is>
+      </c>
       <c r="I107" s="2" t="inlineStr"/>
-      <c r="J107" s="3" t="inlineStr"/>
-      <c r="K107" s="2" t="inlineStr"/>
+      <c r="J107" s="3" t="inlineStr">
+        <is>
+          <t>2897005</t>
+        </is>
+      </c>
+      <c r="K107" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001107</t>
+          <t>ARI:0001108</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>Immune thrombocytopenia</t>
+          <t>Immunoglobulin A vasculitis</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>2897005</t>
+          <t>191306005</t>
         </is>
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
-          <t>Immune thrombocytopenia</t>
+          <t>Immunoglobulin A vasculitis</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
@@ -5763,13 +5735,13 @@
       </c>
       <c r="H108" s="4" t="inlineStr">
         <is>
-          <t>4103532</t>
+          <t>4101602</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr"/>
       <c r="J108" s="3" t="inlineStr">
         <is>
-          <t>13172003, 128092005, 2897005, 438476003, 32273002, 128091003</t>
+          <t>191306005</t>
         </is>
       </c>
       <c r="K108" s="5" t="inlineStr">
@@ -5781,22 +5753,22 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001108</t>
+          <t>ARI:0001109</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>Immunoglobulin A vasculitis</t>
+          <t>Immunoglobulin G4 related disease</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>191306005</t>
+          <t>10743271000119103</t>
         </is>
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t>Immunoglobulin A vasculitis</t>
+          <t>Immunoglobulin G4 related disease</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
@@ -5816,13 +5788,13 @@
       </c>
       <c r="H109" s="4" t="inlineStr">
         <is>
-          <t>4101602</t>
+          <t>36717255</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr"/>
       <c r="J109" s="3" t="inlineStr">
         <is>
-          <t>191306005</t>
+          <t>10743271000119103</t>
         </is>
       </c>
       <c r="K109" s="5" t="inlineStr">
@@ -5834,22 +5806,22 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001109</t>
+          <t>ARI:0001110</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>Immunoglobulin G4 related disease</t>
+          <t>Immunoglobulin G4 related ophthalmic disease</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>10743271000119103</t>
+          <t>1187510006</t>
         </is>
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
-          <t>Immunoglobulin G4 related disease</t>
+          <t>Immunoglobulin G4 related ophthalmic disease</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
@@ -5869,13 +5841,13 @@
       </c>
       <c r="H110" s="4" t="inlineStr">
         <is>
-          <t>36717255</t>
+          <t>37162346</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr"/>
       <c r="J110" s="3" t="inlineStr">
         <is>
-          <t>10743271000119103, 234549008, 722870008</t>
+          <t>1187510006</t>
         </is>
       </c>
       <c r="K110" s="5" t="inlineStr">
@@ -5887,22 +5859,22 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001110</t>
+          <t>ARI:0001111</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>Immunoglobulin G4 related ophthalmic disease</t>
+          <t>Inclusion body myositis</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>1187510006</t>
+          <t>72315009</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>Immunoglobulin G4 related ophthalmic disease</t>
+          <t>Inclusion body myositis</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
@@ -5922,13 +5894,13 @@
       </c>
       <c r="H111" s="4" t="inlineStr">
         <is>
-          <t>37162346</t>
+          <t>4216406</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr"/>
       <c r="J111" s="3" t="inlineStr">
         <is>
-          <t>1187510006</t>
+          <t>72315009</t>
         </is>
       </c>
       <c r="K111" s="5" t="inlineStr">
@@ -5940,27 +5912,27 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001111</t>
+          <t>ARI:0001112</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>Inclusion body myositis</t>
+          <t>Inflammatory Bowel Disease</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>72315009</t>
+          <t>24526004</t>
         </is>
       </c>
       <c r="D112" s="3" t="inlineStr">
         <is>
-          <t>Inclusion body myositis</t>
+          <t>Inflammatory bowel disease</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>0.778</t>
+          <t>0.772</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
@@ -5975,13 +5947,13 @@
       </c>
       <c r="H112" s="4" t="inlineStr">
         <is>
-          <t>4216406</t>
+          <t>4074815</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr"/>
       <c r="J112" s="3" t="inlineStr">
         <is>
-          <t>72315009</t>
+          <t>24526004</t>
         </is>
       </c>
       <c r="K112" s="5" t="inlineStr">
@@ -5993,27 +5965,27 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001112</t>
+          <t>ARI:0001113</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>Inflammatory Bowel Disease</t>
+          <t>Insulin autoimmune syndrome</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>24526004</t>
+          <t>408539000</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>Inflammatory bowel disease</t>
+          <t>Insulin autoimmune syndrome</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>0.772</t>
+          <t>0.778</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
@@ -6028,13 +6000,13 @@
       </c>
       <c r="H113" s="4" t="inlineStr">
         <is>
-          <t>4074815</t>
+          <t>4252384</t>
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr"/>
       <c r="J113" s="3" t="inlineStr">
         <is>
-          <t>24526004</t>
+          <t>408539000</t>
         </is>
       </c>
       <c r="K113" s="5" t="inlineStr">
@@ -6046,22 +6018,22 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001113</t>
+          <t>ARI:0001114</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>Insulin autoimmune syndrome</t>
+          <t>Insulin resistance - type B</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>408539000</t>
+          <t>237652003</t>
         </is>
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
-          <t>Insulin autoimmune syndrome</t>
+          <t>Insulin resistance - type B</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
@@ -6081,13 +6053,13 @@
       </c>
       <c r="H114" s="4" t="inlineStr">
         <is>
-          <t>4252384</t>
+          <t>4129525</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr"/>
       <c r="J114" s="3" t="inlineStr">
         <is>
-          <t>408539000</t>
+          <t>237652003</t>
         </is>
       </c>
       <c r="K114" s="5" t="inlineStr">
@@ -6099,22 +6071,22 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001114</t>
+          <t>ARI:0001115</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>Insulin resistance - type B</t>
+          <t>Intermediate uveitis</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>237652003</t>
+          <t>314429009</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>Insulin resistance - type B</t>
+          <t>Intermediate uveitis</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
@@ -6134,13 +6106,13 @@
       </c>
       <c r="H115" s="4" t="inlineStr">
         <is>
-          <t>4129525</t>
+          <t>4197155</t>
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr"/>
       <c r="J115" s="3" t="inlineStr">
         <is>
-          <t>237652003</t>
+          <t>314429009</t>
         </is>
       </c>
       <c r="K115" s="5" t="inlineStr">
@@ -6152,22 +6124,22 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001115</t>
+          <t>ARI:0001116</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>Intermediate uveitis</t>
+          <t>Interstitial lung disease</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>314429009</t>
+          <t>233703007</t>
         </is>
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
-          <t>Intermediate uveitis</t>
+          <t>Interstitial lung disease</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
@@ -6187,13 +6159,13 @@
       </c>
       <c r="H116" s="4" t="inlineStr">
         <is>
-          <t>4197155</t>
+          <t>4119786</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr"/>
       <c r="J116" s="3" t="inlineStr">
         <is>
-          <t>314429009, 1231232007, 45688009</t>
+          <t>233703007</t>
         </is>
       </c>
       <c r="K116" s="5" t="inlineStr">
@@ -6205,22 +6177,22 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001116</t>
+          <t>ARI:0001117</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>Interstitial lung disease</t>
+          <t>Juvenile Rheumatoid Arthritis</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>233703007</t>
+          <t>410502007</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr">
         <is>
-          <t>Interstitial lung disease</t>
+          <t>Juvenile idiopathic arthritis</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
@@ -6235,45 +6207,41 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>(preferred name)</t>
+          <t>Juvenile idiopathic arthritis</t>
         </is>
       </c>
       <c r="H117" s="4" t="inlineStr">
         <is>
-          <t>4119786</t>
+          <t>4259507</t>
         </is>
       </c>
       <c r="I117" s="2" t="inlineStr"/>
       <c r="J117" s="3" t="inlineStr">
         <is>
-          <t>233703007</t>
-        </is>
-      </c>
-      <c r="K117" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>239796000, 410795001</t>
+        </is>
+      </c>
+      <c r="K117" s="2" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001117</t>
+          <t>ARI:0001118</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>Juvenile Rheumatoid Arthritis</t>
+          <t>Lichen planus</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>410502007</t>
+          <t>4776004</t>
         </is>
       </c>
       <c r="D118" s="3" t="inlineStr">
         <is>
-          <t>Juvenile idiopathic arthritis</t>
+          <t>Lichen planus</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
@@ -6288,41 +6256,45 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>Juvenile idiopathic arthritis</t>
+          <t>(preferred name)</t>
         </is>
       </c>
       <c r="H118" s="4" t="inlineStr">
         <is>
-          <t>4259507</t>
+          <t>132703</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr"/>
       <c r="J118" s="3" t="inlineStr">
         <is>
-          <t>410795001, 239796000</t>
-        </is>
-      </c>
-      <c r="K118" s="2" t="inlineStr"/>
+          <t>4776004</t>
+        </is>
+      </c>
+      <c r="K118" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001118</t>
+          <t>ARI:0001119</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>Lichen planus</t>
+          <t>Lichen sclerosus</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>4776004</t>
+          <t>895454001</t>
         </is>
       </c>
       <c r="D119" s="3" t="inlineStr">
         <is>
-          <t>Lichen planus</t>
+          <t>Lichen sclerosus</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
@@ -6342,13 +6314,13 @@
       </c>
       <c r="H119" s="4" t="inlineStr">
         <is>
-          <t>132703</t>
+          <t>619430</t>
         </is>
       </c>
       <c r="I119" s="2" t="inlineStr"/>
       <c r="J119" s="3" t="inlineStr">
         <is>
-          <t>4776004</t>
+          <t>895454001, 25674000</t>
         </is>
       </c>
       <c r="K119" s="5" t="inlineStr">
@@ -6360,22 +6332,22 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001119</t>
+          <t>ARI:0001120</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>Lichen sclerosus</t>
+          <t>Ligneous conjunctivitis</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>895454001</t>
+          <t>403435005</t>
         </is>
       </c>
       <c r="D120" s="3" t="inlineStr">
         <is>
-          <t>Lichen sclerosus</t>
+          <t>Ligneous conjunctivitis</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
@@ -6395,13 +6367,13 @@
       </c>
       <c r="H120" s="4" t="inlineStr">
         <is>
-          <t>619430</t>
+          <t>4296491</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr"/>
       <c r="J120" s="3" t="inlineStr">
         <is>
-          <t>895454001, 25674000</t>
+          <t>403435005</t>
         </is>
       </c>
       <c r="K120" s="5" t="inlineStr">
@@ -6413,22 +6385,22 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001120</t>
+          <t>ARI:0001121</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>Ligneous conjunctivitis</t>
+          <t>Limbic encephalitis</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>403435005</t>
+          <t>230192003</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
-          <t>Ligneous conjunctivitis</t>
+          <t>Limbic encephalitis</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
@@ -6448,13 +6420,13 @@
       </c>
       <c r="H121" s="4" t="inlineStr">
         <is>
-          <t>4296491</t>
+          <t>4041673</t>
         </is>
       </c>
       <c r="I121" s="2" t="inlineStr"/>
       <c r="J121" s="3" t="inlineStr">
         <is>
-          <t>403435005</t>
+          <t>230192003</t>
         </is>
       </c>
       <c r="K121" s="5" t="inlineStr">
@@ -6466,22 +6438,22 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001121</t>
+          <t>ARI:0001122</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>Limbic encephalitis</t>
+          <t>Limbic encephalitis with dipeptidyl-peptidase 6 antibodies</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>230192003</t>
+          <t>773395008</t>
         </is>
       </c>
       <c r="D122" s="3" t="inlineStr">
         <is>
-          <t>Limbic encephalitis</t>
+          <t>Limbic encephalitis with dipeptidyl-peptidase 6 antibodies</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
@@ -6501,13 +6473,13 @@
       </c>
       <c r="H122" s="4" t="inlineStr">
         <is>
-          <t>4041673</t>
+          <t>36676495</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr"/>
       <c r="J122" s="3" t="inlineStr">
         <is>
-          <t>230192003</t>
+          <t>773395008</t>
         </is>
       </c>
       <c r="K122" s="5" t="inlineStr">
@@ -6519,22 +6491,22 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001122</t>
+          <t>ARI:0001123</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>Limbic encephalitis with dipeptidyl-peptidase 6 antibodies</t>
+          <t>Limbic encephalitis with leucine-rich glioma-inactivated 1 antibodies</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>773395008</t>
+          <t>763794005</t>
         </is>
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
-          <t>Limbic encephalitis with dipeptidyl-peptidase 6 antibodies</t>
+          <t>Limbic encephalitis with leucine-rich glioma-inactivated 1 antibodies</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
@@ -6554,13 +6526,13 @@
       </c>
       <c r="H123" s="4" t="inlineStr">
         <is>
-          <t>36676495</t>
+          <t>35607961</t>
         </is>
       </c>
       <c r="I123" s="2" t="inlineStr"/>
       <c r="J123" s="3" t="inlineStr">
         <is>
-          <t>773395008</t>
+          <t>763794005</t>
         </is>
       </c>
       <c r="K123" s="5" t="inlineStr">
@@ -6572,22 +6544,22 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001123</t>
+          <t>ARI:0001124</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>Limbic encephalitis with leucine-rich glioma-inactivated 1 antibodies</t>
+          <t>Linear IgA dermatosis</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>763794005</t>
+          <t>95330001</t>
         </is>
       </c>
       <c r="D124" s="3" t="inlineStr">
         <is>
-          <t>Limbic encephalitis with leucine-rich glioma-inactivated 1 antibodies</t>
+          <t>Linear IgA dermatosis</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
@@ -6607,13 +6579,13 @@
       </c>
       <c r="H124" s="4" t="inlineStr">
         <is>
-          <t>35607961</t>
+          <t>4317262</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr"/>
       <c r="J124" s="3" t="inlineStr">
         <is>
-          <t>763794005</t>
+          <t>95330001</t>
         </is>
       </c>
       <c r="K124" s="5" t="inlineStr">
@@ -6625,22 +6597,22 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001124</t>
+          <t>ARI:0001125</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>Linear IgA dermatosis</t>
+          <t>Lipomatosis dolorosa</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>95330001</t>
+          <t>71404003</t>
         </is>
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
-          <t>Linear IgA dermatosis</t>
+          <t>Lipomatosis dolorosa</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
@@ -6660,13 +6632,13 @@
       </c>
       <c r="H125" s="4" t="inlineStr">
         <is>
-          <t>4317262</t>
+          <t>4324974</t>
         </is>
       </c>
       <c r="I125" s="2" t="inlineStr"/>
       <c r="J125" s="3" t="inlineStr">
         <is>
-          <t>95330001</t>
+          <t>71404003</t>
         </is>
       </c>
       <c r="K125" s="5" t="inlineStr">
@@ -6678,22 +6650,22 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001125</t>
+          <t>ARI:0001126</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>Lipomatosis dolorosa</t>
+          <t>Lupus vasculitis</t>
         </is>
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>71404003</t>
+          <t>239944008</t>
         </is>
       </c>
       <c r="D126" s="3" t="inlineStr">
         <is>
-          <t>Lipomatosis dolorosa</t>
+          <t>Lupus vasculitis</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
@@ -6713,13 +6685,13 @@
       </c>
       <c r="H126" s="4" t="inlineStr">
         <is>
-          <t>4324974</t>
+          <t>4344495</t>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr"/>
       <c r="J126" s="3" t="inlineStr">
         <is>
-          <t>71404003</t>
+          <t>239944008</t>
         </is>
       </c>
       <c r="K126" s="5" t="inlineStr">
@@ -6731,104 +6703,104 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001126</t>
+          <t>ARI:0001127</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>Lupus vasculitis</t>
-        </is>
-      </c>
-      <c r="C127" s="4" t="inlineStr">
-        <is>
-          <t>239944008</t>
-        </is>
-      </c>
-      <c r="D127" s="3" t="inlineStr">
-        <is>
-          <t>Lupus vasculitis</t>
-        </is>
-      </c>
-      <c r="E127" s="2" t="inlineStr">
-        <is>
-          <t>0.778</t>
-        </is>
-      </c>
-      <c r="F127" s="2" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
+          <t>Male infertility associated with antisperm antibodies</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr"/>
+      <c r="D127" s="3" t="inlineStr"/>
+      <c r="E127" s="2" t="inlineStr"/>
+      <c r="F127" s="2" t="inlineStr"/>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>(preferred name)</t>
-        </is>
-      </c>
-      <c r="H127" s="4" t="inlineStr">
-        <is>
-          <t>4344495</t>
-        </is>
-      </c>
+          <t>no match</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr"/>
       <c r="I127" s="2" t="inlineStr"/>
       <c r="J127" s="3" t="inlineStr">
         <is>
-          <t>239944008</t>
-        </is>
-      </c>
-      <c r="K127" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>414643008</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001127</t>
+          <t>ARI:0001128</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>Male infertility associated with antisperm antibodies</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr"/>
-      <c r="D128" s="3" t="inlineStr"/>
-      <c r="E128" s="2" t="inlineStr"/>
-      <c r="F128" s="2" t="inlineStr"/>
+          <t>Microscopic colitis</t>
+        </is>
+      </c>
+      <c r="C128" s="4" t="inlineStr">
+        <is>
+          <t>235753003</t>
+        </is>
+      </c>
+      <c r="D128" s="3" t="inlineStr">
+        <is>
+          <t>Microscopic colitis</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>0.778</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>no match</t>
-        </is>
-      </c>
-      <c r="H128" s="2" t="inlineStr"/>
+          <t>(preferred name)</t>
+        </is>
+      </c>
+      <c r="H128" s="4" t="inlineStr">
+        <is>
+          <t>4340799</t>
+        </is>
+      </c>
       <c r="I128" s="2" t="inlineStr"/>
       <c r="J128" s="3" t="inlineStr">
         <is>
-          <t>414643008</t>
-        </is>
-      </c>
-      <c r="K128" s="2" t="inlineStr"/>
+          <t>235753003</t>
+        </is>
+      </c>
+      <c r="K128" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001128</t>
+          <t>ARI:0001129</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>Microscopic colitis</t>
+          <t>Microscopic polyangiitis</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>235753003</t>
+          <t>1144805008</t>
         </is>
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
-          <t>Microscopic colitis</t>
+          <t>Microscopic polyangiitis</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
@@ -6848,13 +6820,13 @@
       </c>
       <c r="H129" s="4" t="inlineStr">
         <is>
-          <t>4340799</t>
+          <t>606328</t>
         </is>
       </c>
       <c r="I129" s="2" t="inlineStr"/>
       <c r="J129" s="3" t="inlineStr">
         <is>
-          <t>235753003</t>
+          <t>1144805008</t>
         </is>
       </c>
       <c r="K129" s="5" t="inlineStr">
@@ -6866,22 +6838,22 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001129</t>
+          <t>ARI:0001130</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>Microscopic polyangiitis</t>
+          <t>Mixed collagen vascular disease</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr">
         <is>
-          <t>1144805008</t>
+          <t>398049005</t>
         </is>
       </c>
       <c r="D130" s="3" t="inlineStr">
         <is>
-          <t>Microscopic polyangiitis</t>
+          <t>Mixed collagen vascular disease</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
@@ -6901,13 +6873,13 @@
       </c>
       <c r="H130" s="4" t="inlineStr">
         <is>
-          <t>606328</t>
+          <t>4134867</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr"/>
       <c r="J130" s="3" t="inlineStr">
         <is>
-          <t>1144805008</t>
+          <t>398049005</t>
         </is>
       </c>
       <c r="K130" s="5" t="inlineStr">
@@ -6919,22 +6891,22 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001130</t>
+          <t>ARI:0001131</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>Mixed collagen vascular disease</t>
+          <t>Mooren's ulcer</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>398049005</t>
+          <t>22440001</t>
         </is>
       </c>
       <c r="D131" s="3" t="inlineStr">
         <is>
-          <t>Mixed collagen vascular disease</t>
+          <t>Mooren's ulcer</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
@@ -6954,13 +6926,13 @@
       </c>
       <c r="H131" s="4" t="inlineStr">
         <is>
-          <t>4134867</t>
+          <t>435271</t>
         </is>
       </c>
       <c r="I131" s="2" t="inlineStr"/>
       <c r="J131" s="3" t="inlineStr">
         <is>
-          <t>398049005</t>
+          <t>22440001</t>
         </is>
       </c>
       <c r="K131" s="5" t="inlineStr">
@@ -6972,22 +6944,22 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001131</t>
+          <t>ARI:0001132</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>Mooren's ulcer</t>
+          <t>Morphea</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>22440001</t>
+          <t>201049004</t>
         </is>
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
-          <t>Mooren's ulcer</t>
+          <t>Morphea</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
@@ -7007,13 +6979,13 @@
       </c>
       <c r="H132" s="4" t="inlineStr">
         <is>
-          <t>435271</t>
+          <t>4066845</t>
         </is>
       </c>
       <c r="I132" s="2" t="inlineStr"/>
       <c r="J132" s="3" t="inlineStr">
         <is>
-          <t>22440001</t>
+          <t>201049004, 201048007</t>
         </is>
       </c>
       <c r="K132" s="5" t="inlineStr">
@@ -7025,22 +6997,22 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001132</t>
+          <t>ARI:0001133</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>Morphea</t>
+          <t>Motor neuropathy with multiple conduction block</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>201049004</t>
+          <t>230591002</t>
         </is>
       </c>
       <c r="D133" s="3" t="inlineStr">
         <is>
-          <t>Morphea</t>
+          <t>Motor neuropathy with multiple conduction block</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
@@ -7060,13 +7032,13 @@
       </c>
       <c r="H133" s="4" t="inlineStr">
         <is>
-          <t>4066845</t>
+          <t>4046338</t>
         </is>
       </c>
       <c r="I133" s="2" t="inlineStr"/>
       <c r="J133" s="3" t="inlineStr">
         <is>
-          <t>201048007, 201049004</t>
+          <t>230591002</t>
         </is>
       </c>
       <c r="K133" s="5" t="inlineStr">
@@ -7078,22 +7050,22 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001133</t>
+          <t>ARI:0001134</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>Motor neuropathy with multiple conduction block</t>
+          <t>Moyamoya disease</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>230591002</t>
+          <t>69116000</t>
         </is>
       </c>
       <c r="D134" s="3" t="inlineStr">
         <is>
-          <t>Motor neuropathy with multiple conduction block</t>
+          <t>Moyamoya disease</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
@@ -7113,13 +7085,13 @@
       </c>
       <c r="H134" s="4" t="inlineStr">
         <is>
-          <t>4046338</t>
+          <t>378774</t>
         </is>
       </c>
       <c r="I134" s="2" t="inlineStr"/>
       <c r="J134" s="3" t="inlineStr">
         <is>
-          <t>230591002</t>
+          <t>69116000</t>
         </is>
       </c>
       <c r="K134" s="5" t="inlineStr">
@@ -7131,22 +7103,22 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001134</t>
+          <t>ARI:0001135</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>Moyamoya disease</t>
+          <t>Multiple sclerosis</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>69116000</t>
+          <t>24700007</t>
         </is>
       </c>
       <c r="D135" s="3" t="inlineStr">
         <is>
-          <t>Moyamoya disease</t>
+          <t>Multiple sclerosis</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
@@ -7166,13 +7138,13 @@
       </c>
       <c r="H135" s="4" t="inlineStr">
         <is>
-          <t>378774</t>
+          <t>374919</t>
         </is>
       </c>
       <c r="I135" s="2" t="inlineStr"/>
       <c r="J135" s="3" t="inlineStr">
         <is>
-          <t>69116000</t>
+          <t>24700007</t>
         </is>
       </c>
       <c r="K135" s="5" t="inlineStr">
@@ -7184,22 +7156,22 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001135</t>
+          <t>ARI:0001136</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>Multiple sclerosis</t>
+          <t>Myasthenia gravis</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
-          <t>24700007</t>
+          <t>91637004</t>
         </is>
       </c>
       <c r="D136" s="3" t="inlineStr">
         <is>
-          <t>Multiple sclerosis</t>
+          <t>Myasthenia gravis</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
@@ -7219,13 +7191,13 @@
       </c>
       <c r="H136" s="4" t="inlineStr">
         <is>
-          <t>374919</t>
+          <t>76685</t>
         </is>
       </c>
       <c r="I136" s="2" t="inlineStr"/>
       <c r="J136" s="3" t="inlineStr">
         <is>
-          <t>24700007, 428700003, 426373005, 49692006, 128460000</t>
+          <t>91637004</t>
         </is>
       </c>
       <c r="K136" s="5" t="inlineStr">
@@ -7237,22 +7209,22 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001136</t>
+          <t>ARI:0001137</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>Myasthenia gravis</t>
+          <t>Myelin oligodendrocyte glycoprotein antibody-associated disease</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>91637004</t>
+          <t>1237194006</t>
         </is>
       </c>
       <c r="D137" s="3" t="inlineStr">
         <is>
-          <t>Myasthenia gravis</t>
+          <t>Myelin oligodendrocyte glycoprotein antibody-associated disease</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
@@ -7272,13 +7244,13 @@
       </c>
       <c r="H137" s="4" t="inlineStr">
         <is>
-          <t>76685</t>
+          <t>37164973</t>
         </is>
       </c>
       <c r="I137" s="2" t="inlineStr"/>
       <c r="J137" s="3" t="inlineStr">
         <is>
-          <t>91637004</t>
+          <t>718213001, 1237194006</t>
         </is>
       </c>
       <c r="K137" s="5" t="inlineStr">
@@ -7290,22 +7262,22 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001137</t>
+          <t>ARI:0001138</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>Myelin oligodendrocyte glycoprotein antibody-associated disease</t>
+          <t>Myocarditis due to autoimmune disease</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>1237194006</t>
+          <t>871640001</t>
         </is>
       </c>
       <c r="D138" s="3" t="inlineStr">
         <is>
-          <t>Myelin oligodendrocyte glycoprotein antibody-associated disease</t>
+          <t>Myocarditis due to autoimmune disease</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
@@ -7325,13 +7297,13 @@
       </c>
       <c r="H138" s="4" t="inlineStr">
         <is>
-          <t>37164973</t>
+          <t>3656114</t>
         </is>
       </c>
       <c r="I138" s="2" t="inlineStr"/>
       <c r="J138" s="3" t="inlineStr">
         <is>
-          <t>1237194006, 718213001</t>
+          <t>871640001, 37217002</t>
         </is>
       </c>
       <c r="K138" s="5" t="inlineStr">
@@ -7343,22 +7315,22 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001138</t>
+          <t>ARI:0001139</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>Myocarditis due to autoimmune disease</t>
+          <t>Myositis</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>871640001</t>
+          <t>26889001</t>
         </is>
       </c>
       <c r="D139" s="3" t="inlineStr">
         <is>
-          <t>Myocarditis due to autoimmune disease</t>
+          <t>Myositis</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
@@ -7378,13 +7350,13 @@
       </c>
       <c r="H139" s="4" t="inlineStr">
         <is>
-          <t>3656114</t>
+          <t>73001</t>
         </is>
       </c>
       <c r="I139" s="2" t="inlineStr"/>
       <c r="J139" s="3" t="inlineStr">
         <is>
-          <t>871640001, 37217002</t>
+          <t>26889001</t>
         </is>
       </c>
       <c r="K139" s="5" t="inlineStr">
@@ -7396,22 +7368,22 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001139</t>
+          <t>ARI:0001140</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>Myositis</t>
+          <t>Necrotizing vasculitis</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr">
         <is>
-          <t>26889001</t>
+          <t>11791001</t>
         </is>
       </c>
       <c r="D140" s="3" t="inlineStr">
         <is>
-          <t>Myositis</t>
+          <t>Necrotizing vasculitis</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
@@ -7431,13 +7403,13 @@
       </c>
       <c r="H140" s="4" t="inlineStr">
         <is>
-          <t>73001</t>
+          <t>4039691</t>
         </is>
       </c>
       <c r="I140" s="2" t="inlineStr"/>
       <c r="J140" s="3" t="inlineStr">
         <is>
-          <t>722991004, 715863001, 702380008, 26889001</t>
+          <t>11791001</t>
         </is>
       </c>
       <c r="K140" s="5" t="inlineStr">
@@ -7449,22 +7421,22 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001140</t>
+          <t>ARI:0001141</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>Necrotizing vasculitis</t>
+          <t>Neonatal lupus erythematosus</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>11791001</t>
+          <t>95609003</t>
         </is>
       </c>
       <c r="D141" s="3" t="inlineStr">
         <is>
-          <t>Necrotizing vasculitis</t>
+          <t>Neonatal lupus erythematosus</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
@@ -7484,13 +7456,13 @@
       </c>
       <c r="H141" s="4" t="inlineStr">
         <is>
-          <t>4039691</t>
+          <t>4316373</t>
         </is>
       </c>
       <c r="I141" s="2" t="inlineStr"/>
       <c r="J141" s="3" t="inlineStr">
         <is>
-          <t>11791001</t>
+          <t>95609003</t>
         </is>
       </c>
       <c r="K141" s="5" t="inlineStr">
@@ -7502,22 +7474,22 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001141</t>
+          <t>ARI:0001142</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t>Neonatal lupus erythematosus</t>
+          <t>Neuralgic amyotrophy</t>
         </is>
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>95609003</t>
+          <t>26609002</t>
         </is>
       </c>
       <c r="D142" s="3" t="inlineStr">
         <is>
-          <t>Neonatal lupus erythematosus</t>
+          <t>Neuralgic amyotrophy</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
@@ -7537,13 +7509,13 @@
       </c>
       <c r="H142" s="4" t="inlineStr">
         <is>
-          <t>4316373</t>
+          <t>377271</t>
         </is>
       </c>
       <c r="I142" s="2" t="inlineStr"/>
       <c r="J142" s="3" t="inlineStr">
         <is>
-          <t>95609003</t>
+          <t>26609002</t>
         </is>
       </c>
       <c r="K142" s="5" t="inlineStr">
@@ -7555,22 +7527,22 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001142</t>
+          <t>ARI:0001143</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>Neuralgic amyotrophy</t>
+          <t>Neuromyelitis optica</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>26609002</t>
+          <t>25044007</t>
         </is>
       </c>
       <c r="D143" s="3" t="inlineStr">
         <is>
-          <t>Neuralgic amyotrophy</t>
+          <t>Neuromyelitis optica</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
@@ -7590,13 +7562,13 @@
       </c>
       <c r="H143" s="4" t="inlineStr">
         <is>
-          <t>377271</t>
+          <t>380995</t>
         </is>
       </c>
       <c r="I143" s="2" t="inlineStr"/>
       <c r="J143" s="3" t="inlineStr">
         <is>
-          <t>3548001, 26609002</t>
+          <t>25044007</t>
         </is>
       </c>
       <c r="K143" s="5" t="inlineStr">
@@ -7608,22 +7580,22 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001143</t>
+          <t>ARI:0001144</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t>Neuromyelitis optica</t>
+          <t>Neuromyotonia</t>
         </is>
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
-          <t>25044007</t>
+          <t>305719002</t>
         </is>
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
-          <t>Neuromyelitis optica</t>
+          <t>Neuromyotonia</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
@@ -7643,13 +7615,13 @@
       </c>
       <c r="H144" s="4" t="inlineStr">
         <is>
-          <t>380995</t>
+          <t>4125693</t>
         </is>
       </c>
       <c r="I144" s="2" t="inlineStr"/>
       <c r="J144" s="3" t="inlineStr">
         <is>
-          <t>25044007</t>
+          <t>305719002</t>
         </is>
       </c>
       <c r="K144" s="5" t="inlineStr">
@@ -7661,104 +7633,104 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001144</t>
+          <t>ARI:0001145</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>Neuromyotonia</t>
-        </is>
-      </c>
-      <c r="C145" s="4" t="inlineStr">
-        <is>
-          <t>305719002</t>
-        </is>
-      </c>
-      <c r="D145" s="3" t="inlineStr">
-        <is>
-          <t>Neuromyotonia</t>
-        </is>
-      </c>
-      <c r="E145" s="2" t="inlineStr">
-        <is>
-          <t>0.778</t>
-        </is>
-      </c>
-      <c r="F145" s="2" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
+          <t>Ocular myasthenia gravis</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr"/>
+      <c r="D145" s="3" t="inlineStr"/>
+      <c r="E145" s="2" t="inlineStr"/>
+      <c r="F145" s="2" t="inlineStr"/>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>(preferred name)</t>
-        </is>
-      </c>
-      <c r="H145" s="4" t="inlineStr">
-        <is>
-          <t>4125693</t>
-        </is>
-      </c>
+          <t>no match</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr"/>
       <c r="I145" s="2" t="inlineStr"/>
       <c r="J145" s="3" t="inlineStr">
         <is>
-          <t>305719002</t>
-        </is>
-      </c>
-      <c r="K145" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>230684008</t>
+        </is>
+      </c>
+      <c r="K145" s="2" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001145</t>
+          <t>ARI:0001146</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>Ocular myasthenia gravis</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr"/>
-      <c r="D146" s="3" t="inlineStr"/>
-      <c r="E146" s="2" t="inlineStr"/>
-      <c r="F146" s="2" t="inlineStr"/>
+          <t>Ophthalmoplegia due to Graves' disease</t>
+        </is>
+      </c>
+      <c r="C146" s="4" t="inlineStr">
+        <is>
+          <t>104461000119104</t>
+        </is>
+      </c>
+      <c r="D146" s="3" t="inlineStr">
+        <is>
+          <t>Ophthalmoplegia due to Graves' disease</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>0.778</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>no match</t>
-        </is>
-      </c>
-      <c r="H146" s="2" t="inlineStr"/>
+          <t>(preferred name)</t>
+        </is>
+      </c>
+      <c r="H146" s="4" t="inlineStr">
+        <is>
+          <t>45757069</t>
+        </is>
+      </c>
       <c r="I146" s="2" t="inlineStr"/>
       <c r="J146" s="3" t="inlineStr">
         <is>
-          <t>230684008</t>
-        </is>
-      </c>
-      <c r="K146" s="2" t="inlineStr"/>
+          <t>104461000119104</t>
+        </is>
+      </c>
+      <c r="K146" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001146</t>
+          <t>ARI:0001147</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>Ophthalmoplegia due to Graves' disease</t>
+          <t>Opsoclonus-myoclonus syndrome</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>104461000119104</t>
+          <t>230350000</t>
         </is>
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
-          <t>Ophthalmoplegia due to Graves' disease</t>
+          <t>Opsoclonus-myoclonus syndrome</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
@@ -7778,13 +7750,13 @@
       </c>
       <c r="H147" s="4" t="inlineStr">
         <is>
-          <t>45757069</t>
+          <t>4043399</t>
         </is>
       </c>
       <c r="I147" s="2" t="inlineStr"/>
       <c r="J147" s="3" t="inlineStr">
         <is>
-          <t>104461000119104, 276177000</t>
+          <t>230350000</t>
         </is>
       </c>
       <c r="K147" s="5" t="inlineStr">
@@ -7796,22 +7768,22 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001147</t>
+          <t>ARI:0001148</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>Opsoclonus-myoclonus syndrome</t>
+          <t>Palindromic rheumatism</t>
         </is>
       </c>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>230350000</t>
+          <t>50442003</t>
         </is>
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
-          <t>Opsoclonus-myoclonus syndrome</t>
+          <t>Palindromic rheumatism</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
@@ -7831,13 +7803,13 @@
       </c>
       <c r="H148" s="4" t="inlineStr">
         <is>
-          <t>4043399</t>
+          <t>76196</t>
         </is>
       </c>
       <c r="I148" s="2" t="inlineStr"/>
       <c r="J148" s="3" t="inlineStr">
         <is>
-          <t>230350000</t>
+          <t>50442003</t>
         </is>
       </c>
       <c r="K148" s="5" t="inlineStr">
@@ -7849,22 +7821,22 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001148</t>
+          <t>ARI:0001149</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>Palindromic rheumatism</t>
+          <t>Paraneoplastic cerebellar degeneration</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>50442003</t>
+          <t>192877007</t>
         </is>
       </c>
       <c r="D149" s="3" t="inlineStr">
         <is>
-          <t>Palindromic rheumatism</t>
+          <t>Paraneoplastic cerebellar degeneration</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
@@ -7884,13 +7856,13 @@
       </c>
       <c r="H149" s="4" t="inlineStr">
         <is>
-          <t>76196</t>
+          <t>4102330</t>
         </is>
       </c>
       <c r="I149" s="2" t="inlineStr"/>
       <c r="J149" s="3" t="inlineStr">
         <is>
-          <t>50442003</t>
+          <t>192877007</t>
         </is>
       </c>
       <c r="K149" s="5" t="inlineStr">
@@ -7902,100 +7874,100 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001149</t>
+          <t>ARI:0001150</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t>Paraneoplastic cerebellar degeneration</t>
-        </is>
-      </c>
-      <c r="C150" s="4" t="inlineStr">
-        <is>
-          <t>192877007</t>
-        </is>
-      </c>
-      <c r="D150" s="3" t="inlineStr">
-        <is>
-          <t>Paraneoplastic cerebellar degeneration</t>
-        </is>
-      </c>
-      <c r="E150" s="2" t="inlineStr">
-        <is>
-          <t>0.778</t>
-        </is>
-      </c>
-      <c r="F150" s="2" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
+          <t>Paraneoplastic pemphigus</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr"/>
+      <c r="D150" s="3" t="inlineStr"/>
+      <c r="E150" s="2" t="inlineStr"/>
+      <c r="F150" s="2" t="inlineStr"/>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>(preferred name)</t>
-        </is>
-      </c>
-      <c r="H150" s="4" t="inlineStr">
-        <is>
-          <t>4102330</t>
-        </is>
-      </c>
+          <t>no match</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr"/>
       <c r="I150" s="2" t="inlineStr"/>
-      <c r="J150" s="3" t="inlineStr">
-        <is>
-          <t>192877007</t>
-        </is>
-      </c>
-      <c r="K150" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="J150" s="3" t="inlineStr"/>
+      <c r="K150" s="2" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001150</t>
+          <t>ARI:0001151</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>Paraneoplastic pemphigus</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="inlineStr"/>
-      <c r="D151" s="3" t="inlineStr"/>
-      <c r="E151" s="2" t="inlineStr"/>
-      <c r="F151" s="2" t="inlineStr"/>
+          <t>Paroxysmal cold hemoglobinuria</t>
+        </is>
+      </c>
+      <c r="C151" s="4" t="inlineStr">
+        <is>
+          <t>127057004</t>
+        </is>
+      </c>
+      <c r="D151" s="3" t="inlineStr">
+        <is>
+          <t>Paroxysmal cold hemoglobinuria</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>0.778</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>no match</t>
-        </is>
-      </c>
-      <c r="H151" s="2" t="inlineStr"/>
+          <t>(preferred name)</t>
+        </is>
+      </c>
+      <c r="H151" s="4" t="inlineStr">
+        <is>
+          <t>4131917</t>
+        </is>
+      </c>
       <c r="I151" s="2" t="inlineStr"/>
-      <c r="J151" s="3" t="inlineStr"/>
-      <c r="K151" s="2" t="inlineStr"/>
+      <c r="J151" s="3" t="inlineStr">
+        <is>
+          <t>127057004</t>
+        </is>
+      </c>
+      <c r="K151" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001151</t>
+          <t>ARI:0001152</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t>Paroxysmal cold hemoglobinuria</t>
+          <t>Paroxysmal nocturnal hemoglobinuria</t>
         </is>
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>127057004</t>
+          <t>1963002</t>
         </is>
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
-          <t>Paroxysmal cold hemoglobinuria</t>
+          <t>Paroxysmal nocturnal hemoglobinuria</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
@@ -8015,13 +7987,13 @@
       </c>
       <c r="H152" s="4" t="inlineStr">
         <is>
-          <t>4131917</t>
+          <t>4024671</t>
         </is>
       </c>
       <c r="I152" s="2" t="inlineStr"/>
       <c r="J152" s="3" t="inlineStr">
         <is>
-          <t>127057004</t>
+          <t>1963002</t>
         </is>
       </c>
       <c r="K152" s="5" t="inlineStr">
@@ -8033,22 +8005,22 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001152</t>
+          <t>ARI:0001153</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>Paroxysmal nocturnal hemoglobinuria</t>
+          <t>Pediatric autoimmune neuropsychiatric disorder associated with streptococcal infection</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>1963002</t>
+          <t>446682003</t>
         </is>
       </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
-          <t>Paroxysmal nocturnal hemoglobinuria</t>
+          <t>Pediatric autoimmune neuropsychiatric disorder associated with streptococcal infection</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
@@ -8068,13 +8040,13 @@
       </c>
       <c r="H153" s="4" t="inlineStr">
         <is>
-          <t>4024671</t>
+          <t>40488855</t>
         </is>
       </c>
       <c r="I153" s="2" t="inlineStr"/>
       <c r="J153" s="3" t="inlineStr">
         <is>
-          <t>1963002</t>
+          <t>446682003</t>
         </is>
       </c>
       <c r="K153" s="5" t="inlineStr">
@@ -8086,22 +8058,22 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001153</t>
+          <t>ARI:0001154</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t>Pediatric autoimmune neuropsychiatric disorder associated with streptococcal infection</t>
+          <t>Pemphigus</t>
         </is>
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>446682003</t>
+          <t>65172003</t>
         </is>
       </c>
       <c r="D154" s="3" t="inlineStr">
         <is>
-          <t>Pediatric autoimmune neuropsychiatric disorder associated with streptococcal infection</t>
+          <t>Pemphigus</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
@@ -8121,13 +8093,13 @@
       </c>
       <c r="H154" s="4" t="inlineStr">
         <is>
-          <t>40488855</t>
+          <t>135338</t>
         </is>
       </c>
       <c r="I154" s="2" t="inlineStr"/>
       <c r="J154" s="3" t="inlineStr">
         <is>
-          <t>446682003</t>
+          <t>65172003</t>
         </is>
       </c>
       <c r="K154" s="5" t="inlineStr">
@@ -8139,22 +8111,22 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001154</t>
+          <t>ARI:0001155</t>
         </is>
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>Pemphigus</t>
+          <t>POEMS syndrome</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>65172003</t>
+          <t>79268002</t>
         </is>
       </c>
       <c r="D155" s="3" t="inlineStr">
         <is>
-          <t>Pemphigus</t>
+          <t>POEMS syndrome</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
@@ -8174,13 +8146,13 @@
       </c>
       <c r="H155" s="4" t="inlineStr">
         <is>
-          <t>135338</t>
+          <t>4193776</t>
         </is>
       </c>
       <c r="I155" s="2" t="inlineStr"/>
       <c r="J155" s="3" t="inlineStr">
         <is>
-          <t>46459009, 200907003, 65172003, 36739006, 35154004, 402718003, 49420001</t>
+          <t>79268002</t>
         </is>
       </c>
       <c r="K155" s="5" t="inlineStr">
@@ -8192,22 +8164,22 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001155</t>
+          <t>ARI:0001156</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t>POEMS syndrome</t>
+          <t>Polyarteritis nodosa</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>79268002</t>
+          <t>155441006</t>
         </is>
       </c>
       <c r="D156" s="3" t="inlineStr">
         <is>
-          <t>POEMS syndrome</t>
+          <t>Polyarteritis nodosa</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
@@ -8227,13 +8199,13 @@
       </c>
       <c r="H156" s="4" t="inlineStr">
         <is>
-          <t>4193776</t>
+          <t>320749</t>
         </is>
       </c>
       <c r="I156" s="2" t="inlineStr"/>
       <c r="J156" s="3" t="inlineStr">
         <is>
-          <t>79268002</t>
+          <t>155441006</t>
         </is>
       </c>
       <c r="K156" s="5" t="inlineStr">
@@ -8245,48 +8217,48 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001156</t>
+          <t>ARI:0001157</t>
         </is>
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>Polyarteritis nodosa</t>
+          <t>Polyglandular autoimmune syndrome type 1</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>155441006</t>
+          <t>11244009</t>
         </is>
       </c>
       <c r="D157" s="3" t="inlineStr">
         <is>
-          <t>Polyarteritis nodosa</t>
+          <t>Polyglandular autoimmune syndrome, type 1</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>0.778</t>
+          <t>0.556</t>
         </is>
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>synonym</t>
         </is>
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>(preferred name)</t>
+          <t>Whitaker syndrome</t>
         </is>
       </c>
       <c r="H157" s="4" t="inlineStr">
         <is>
-          <t>320749</t>
+          <t>4008545</t>
         </is>
       </c>
       <c r="I157" s="2" t="inlineStr"/>
       <c r="J157" s="3" t="inlineStr">
         <is>
-          <t>155441006</t>
+          <t>11244009</t>
         </is>
       </c>
       <c r="K157" s="5" t="inlineStr">
@@ -8298,22 +8270,22 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001157</t>
+          <t>ARI:0001158</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>Polyglandular autoimmune syndrome type 1</t>
+          <t>Polyglandular autoimmune syndrome type 2</t>
         </is>
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>11244009</t>
+          <t>83728000</t>
         </is>
       </c>
       <c r="D158" s="3" t="inlineStr">
         <is>
-          <t>Polyglandular autoimmune syndrome, type 1</t>
+          <t>Polyglandular autoimmune syndrome, type 2</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
@@ -8328,18 +8300,18 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune polyendocrinopathy-candidiasis-ectodermal dystrophy</t>
+          <t>Schmidt syndrome</t>
         </is>
       </c>
       <c r="H158" s="4" t="inlineStr">
         <is>
-          <t>4008545</t>
+          <t>4308266</t>
         </is>
       </c>
       <c r="I158" s="2" t="inlineStr"/>
       <c r="J158" s="3" t="inlineStr">
         <is>
-          <t>11244009</t>
+          <t>83728000</t>
         </is>
       </c>
       <c r="K158" s="5" t="inlineStr">
@@ -8351,71 +8323,75 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001158</t>
+          <t>ARI:0001159</t>
         </is>
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>Polyglandular autoimmune syndrome type 2</t>
+          <t>Polyglandular autoimmune syndrome type 3</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>403767009</t>
+          <t>449731009</t>
         </is>
       </c>
       <c r="D159" s="3" t="inlineStr">
         <is>
-          <t>Acrocephalopolysyndactyly type II</t>
+          <t>Autoimmune polyendocrine syndrome type 3</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>0.556</t>
+          <t>0.778</t>
         </is>
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t>synonym</t>
+          <t>name</t>
         </is>
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>Carpenter syndrome</t>
+          <t>Autoimmune polyendocrine syndrome type 3</t>
         </is>
       </c>
       <c r="H159" s="4" t="inlineStr">
         <is>
-          <t>4301299</t>
+          <t>42709859</t>
         </is>
       </c>
       <c r="I159" s="2" t="inlineStr"/>
       <c r="J159" s="3" t="inlineStr">
         <is>
-          <t>83728000</t>
-        </is>
-      </c>
-      <c r="K159" s="2" t="inlineStr"/>
+          <t>449731009</t>
+        </is>
+      </c>
+      <c r="K159" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001159</t>
+          <t>ARI:0001160</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t>Polyglandular autoimmune syndrome type 3</t>
+          <t>Polyglandular autoimmune syndrome type 4</t>
         </is>
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>449731009</t>
+          <t>449730005</t>
         </is>
       </c>
       <c r="D160" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune polyendocrine syndrome type 3</t>
+          <t>Autoimmune polyendocrine syndrome type 4</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
@@ -8430,18 +8406,18 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune polyendocrine syndrome type 3</t>
+          <t>Autoimmune polyendocrine syndrome type 4</t>
         </is>
       </c>
       <c r="H160" s="4" t="inlineStr">
         <is>
-          <t>42709859</t>
+          <t>42709858</t>
         </is>
       </c>
       <c r="I160" s="2" t="inlineStr"/>
       <c r="J160" s="3" t="inlineStr">
         <is>
-          <t>449731009</t>
+          <t>449730005</t>
         </is>
       </c>
       <c r="K160" s="5" t="inlineStr">
@@ -8453,22 +8429,22 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001160</t>
+          <t>ARI:0001161</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>Polyglandular autoimmune syndrome type 4</t>
+          <t>Polymyalgia rheumatica</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>449730005</t>
+          <t>65323003</t>
         </is>
       </c>
       <c r="D161" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune polyendocrine syndrome type 4</t>
+          <t>Polymyalgia rheumatica</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
@@ -8483,18 +8459,18 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune polyendocrine syndrome type 4</t>
+          <t>(preferred name)</t>
         </is>
       </c>
       <c r="H161" s="4" t="inlineStr">
         <is>
-          <t>42709858</t>
+          <t>255348</t>
         </is>
       </c>
       <c r="I161" s="2" t="inlineStr"/>
       <c r="J161" s="3" t="inlineStr">
         <is>
-          <t>449730005</t>
+          <t>65323003</t>
         </is>
       </c>
       <c r="K161" s="5" t="inlineStr">
@@ -8506,22 +8482,22 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001161</t>
+          <t>ARI:0001162</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>Polymyalgia rheumatica</t>
+          <t>Polymyositis</t>
         </is>
       </c>
       <c r="C162" s="4" t="inlineStr">
         <is>
-          <t>65323003</t>
+          <t>31384009</t>
         </is>
       </c>
       <c r="D162" s="3" t="inlineStr">
         <is>
-          <t>Polymyalgia rheumatica</t>
+          <t>Polymyositis</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
@@ -8541,13 +8517,13 @@
       </c>
       <c r="H162" s="4" t="inlineStr">
         <is>
-          <t>255348</t>
+          <t>80800</t>
         </is>
       </c>
       <c r="I162" s="2" t="inlineStr"/>
       <c r="J162" s="3" t="inlineStr">
         <is>
-          <t>65323003</t>
+          <t>31384009</t>
         </is>
       </c>
       <c r="K162" s="5" t="inlineStr">
@@ -8559,75 +8535,71 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001162</t>
+          <t>ARI:0001163</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>Polymyositis</t>
+          <t>Postmyocardial infarction syndrome</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>31384009</t>
+          <t>827164008</t>
         </is>
       </c>
       <c r="D163" s="3" t="inlineStr">
         <is>
-          <t>Polymyositis</t>
+          <t>Delayed postmyocardial infarction pericarditis</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>0.778</t>
+          <t>0.556</t>
         </is>
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>synonym</t>
         </is>
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>(preferred name)</t>
+          <t>Dressler's syndrome</t>
         </is>
       </c>
       <c r="H163" s="4" t="inlineStr">
         <is>
-          <t>80800</t>
+          <t>37311078</t>
         </is>
       </c>
       <c r="I163" s="2" t="inlineStr"/>
       <c r="J163" s="3" t="inlineStr">
         <is>
-          <t>31384009</t>
-        </is>
-      </c>
-      <c r="K163" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>66189004</t>
+        </is>
+      </c>
+      <c r="K163" s="2" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001163</t>
+          <t>ARI:0001164</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
         <is>
-          <t>Postmyocardial infarction syndrome</t>
+          <t>Postural orthostatic tachycardia syndrome</t>
         </is>
       </c>
       <c r="C164" s="4" t="inlineStr">
         <is>
-          <t>1258984009</t>
+          <t>371073003</t>
         </is>
       </c>
       <c r="D164" s="3" t="inlineStr">
         <is>
-          <t>Post-cardiac injury syndrome</t>
+          <t>Postural orthostatic tachycardia syndrome</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
@@ -8642,41 +8614,45 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>Post-cardiac injury syndrome</t>
+          <t>(preferred name)</t>
         </is>
       </c>
       <c r="H164" s="4" t="inlineStr">
         <is>
-          <t>37166030</t>
+          <t>4159659</t>
         </is>
       </c>
       <c r="I164" s="2" t="inlineStr"/>
       <c r="J164" s="3" t="inlineStr">
         <is>
-          <t>827164008, 66189004, 58600007, 278536002</t>
-        </is>
-      </c>
-      <c r="K164" s="2" t="inlineStr"/>
+          <t>371073003</t>
+        </is>
+      </c>
+      <c r="K164" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001164</t>
+          <t>ARI:0001165</t>
         </is>
       </c>
       <c r="B165" s="3" t="inlineStr">
         <is>
-          <t>Postural orthostatic tachycardia syndrome</t>
+          <t>Primary acquired chylomicronemia</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>371073003</t>
+          <t>402475008</t>
         </is>
       </c>
       <c r="D165" s="3" t="inlineStr">
         <is>
-          <t>Postural orthostatic tachycardia syndrome</t>
+          <t>Primary acquired chylomicronemia</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
@@ -8696,13 +8672,13 @@
       </c>
       <c r="H165" s="4" t="inlineStr">
         <is>
-          <t>4159659</t>
+          <t>4223495</t>
         </is>
       </c>
       <c r="I165" s="2" t="inlineStr"/>
       <c r="J165" s="3" t="inlineStr">
         <is>
-          <t>371073003</t>
+          <t>402475008</t>
         </is>
       </c>
       <c r="K165" s="5" t="inlineStr">
@@ -8714,22 +8690,22 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001165</t>
+          <t>ARI:0001166</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
         <is>
-          <t>Primary acquired chylomicronemia</t>
+          <t>Primary biliary cholangitis</t>
         </is>
       </c>
       <c r="C166" s="4" t="inlineStr">
         <is>
-          <t>402475008</t>
+          <t>31712002</t>
         </is>
       </c>
       <c r="D166" s="3" t="inlineStr">
         <is>
-          <t>Primary acquired chylomicronemia</t>
+          <t>Primary biliary cholangitis</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
@@ -8749,13 +8725,13 @@
       </c>
       <c r="H166" s="4" t="inlineStr">
         <is>
-          <t>4223495</t>
+          <t>4135822</t>
         </is>
       </c>
       <c r="I166" s="2" t="inlineStr"/>
       <c r="J166" s="3" t="inlineStr">
         <is>
-          <t>402475008</t>
+          <t>31712002</t>
         </is>
       </c>
       <c r="K166" s="5" t="inlineStr">
@@ -8767,22 +8743,22 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001166</t>
+          <t>ARI:0001167</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
         <is>
-          <t>Primary biliary cholangitis</t>
+          <t>Primary idiopathic dilated cardiomyopathy</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>31712002</t>
+          <t>53043001</t>
         </is>
       </c>
       <c r="D167" s="3" t="inlineStr">
         <is>
-          <t>Primary biliary cholangitis</t>
+          <t>Primary idiopathic dilated cardiomyopathy</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
@@ -8802,13 +8778,13 @@
       </c>
       <c r="H167" s="4" t="inlineStr">
         <is>
-          <t>4135822</t>
+          <t>4203149</t>
         </is>
       </c>
       <c r="I167" s="2" t="inlineStr"/>
       <c r="J167" s="3" t="inlineStr">
         <is>
-          <t>31712002</t>
+          <t>53043001</t>
         </is>
       </c>
       <c r="K167" s="5" t="inlineStr">
@@ -8820,22 +8796,22 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001167</t>
+          <t>ARI:0001169</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
         <is>
-          <t>Primary idiopathic dilated cardiomyopathy</t>
+          <t>Primary sclerosing cholangitis</t>
         </is>
       </c>
       <c r="C168" s="4" t="inlineStr">
         <is>
-          <t>53043001</t>
+          <t>197441003</t>
         </is>
       </c>
       <c r="D168" s="3" t="inlineStr">
         <is>
-          <t>Primary idiopathic dilated cardiomyopathy</t>
+          <t>Primary sclerosing cholangitis</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
@@ -8855,13 +8831,13 @@
       </c>
       <c r="H168" s="4" t="inlineStr">
         <is>
-          <t>4203149</t>
+          <t>4058821</t>
         </is>
       </c>
       <c r="I168" s="2" t="inlineStr"/>
       <c r="J168" s="3" t="inlineStr">
         <is>
-          <t>53043001</t>
+          <t>197441003</t>
         </is>
       </c>
       <c r="K168" s="5" t="inlineStr">
@@ -8873,22 +8849,22 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001169</t>
+          <t>ARI:0001170</t>
         </is>
       </c>
       <c r="B169" s="3" t="inlineStr">
         <is>
-          <t>Primary sclerosing cholangitis</t>
+          <t>Progressive hemifacial atrophy</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>197441003</t>
+          <t>718224004</t>
         </is>
       </c>
       <c r="D169" s="3" t="inlineStr">
         <is>
-          <t>Primary sclerosing cholangitis</t>
+          <t>Progressive hemifacial atrophy</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
@@ -8908,13 +8884,13 @@
       </c>
       <c r="H169" s="4" t="inlineStr">
         <is>
-          <t>4058821</t>
+          <t>37397558</t>
         </is>
       </c>
       <c r="I169" s="2" t="inlineStr"/>
       <c r="J169" s="3" t="inlineStr">
         <is>
-          <t>197441003</t>
+          <t>718224004</t>
         </is>
       </c>
       <c r="K169" s="5" t="inlineStr">
@@ -8926,22 +8902,22 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001170</t>
+          <t>ARI:0001171</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
         <is>
-          <t>Progressive hemifacial atrophy</t>
+          <t>Psoriasis</t>
         </is>
       </c>
       <c r="C170" s="4" t="inlineStr">
         <is>
-          <t>718224004</t>
+          <t>9014002</t>
         </is>
       </c>
       <c r="D170" s="3" t="inlineStr">
         <is>
-          <t>Progressive hemifacial atrophy</t>
+          <t>Psoriasis</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
@@ -8961,13 +8937,13 @@
       </c>
       <c r="H170" s="4" t="inlineStr">
         <is>
-          <t>37397558</t>
+          <t>140168</t>
         </is>
       </c>
       <c r="I170" s="2" t="inlineStr"/>
       <c r="J170" s="3" t="inlineStr">
         <is>
-          <t>718224004</t>
+          <t>37042000, 9014002</t>
         </is>
       </c>
       <c r="K170" s="5" t="inlineStr">
@@ -8979,22 +8955,22 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001171</t>
+          <t>ARI:0001172</t>
         </is>
       </c>
       <c r="B171" s="3" t="inlineStr">
         <is>
-          <t>Psoriasis</t>
+          <t>Psoriatic arthritis</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>9014002</t>
+          <t>156370009</t>
         </is>
       </c>
       <c r="D171" s="3" t="inlineStr">
         <is>
-          <t>Psoriasis</t>
+          <t>Psoriatic arthritis</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
@@ -9014,13 +8990,13 @@
       </c>
       <c r="H171" s="4" t="inlineStr">
         <is>
-          <t>140168</t>
+          <t>40319772</t>
         </is>
       </c>
       <c r="I171" s="2" t="inlineStr"/>
       <c r="J171" s="3" t="inlineStr">
         <is>
-          <t>37042000, 9014002</t>
+          <t>33339001, 156370009</t>
         </is>
       </c>
       <c r="K171" s="5" t="inlineStr">
@@ -9032,22 +9008,22 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001172</t>
+          <t>ARI:0001173</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
         <is>
-          <t>Psoriatic arthritis</t>
+          <t>Pure red cell aplasia</t>
         </is>
       </c>
       <c r="C172" s="4" t="inlineStr">
         <is>
-          <t>156370009</t>
+          <t>50715003</t>
         </is>
       </c>
       <c r="D172" s="3" t="inlineStr">
         <is>
-          <t>Psoriatic arthritis</t>
+          <t>Pure red cell aplasia</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
@@ -9067,13 +9043,13 @@
       </c>
       <c r="H172" s="4" t="inlineStr">
         <is>
-          <t>40319772</t>
+          <t>140065</t>
         </is>
       </c>
       <c r="I172" s="2" t="inlineStr"/>
       <c r="J172" s="3" t="inlineStr">
         <is>
-          <t>156370009, 33339001</t>
+          <t>50715003</t>
         </is>
       </c>
       <c r="K172" s="5" t="inlineStr">
@@ -9085,22 +9061,22 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001173</t>
+          <t>ARI:0001174</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
         <is>
-          <t>Pure red cell aplasia</t>
+          <t>Pyoderma gangrenosum</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>50715003</t>
+          <t>74578003</t>
         </is>
       </c>
       <c r="D173" s="3" t="inlineStr">
         <is>
-          <t>Pure red cell aplasia</t>
+          <t>Pyoderma gangrenosum</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
@@ -9120,13 +9096,13 @@
       </c>
       <c r="H173" s="4" t="inlineStr">
         <is>
-          <t>140065</t>
+          <t>133283</t>
         </is>
       </c>
       <c r="I173" s="2" t="inlineStr"/>
       <c r="J173" s="3" t="inlineStr">
         <is>
-          <t>50715003</t>
+          <t>74578003</t>
         </is>
       </c>
       <c r="K173" s="5" t="inlineStr">
@@ -9138,22 +9114,22 @@
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001174</t>
+          <t>ARI:0001175</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
         <is>
-          <t>Pyoderma gangrenosum</t>
+          <t>Rasmussen syndrome</t>
         </is>
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>74578003</t>
+          <t>230191005</t>
         </is>
       </c>
       <c r="D174" s="3" t="inlineStr">
         <is>
-          <t>Pyoderma gangrenosum</t>
+          <t>Rasmussen syndrome</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
@@ -9173,13 +9149,13 @@
       </c>
       <c r="H174" s="4" t="inlineStr">
         <is>
-          <t>133283</t>
+          <t>4041672</t>
         </is>
       </c>
       <c r="I174" s="2" t="inlineStr"/>
       <c r="J174" s="3" t="inlineStr">
         <is>
-          <t>74578003</t>
+          <t>230191005</t>
         </is>
       </c>
       <c r="K174" s="5" t="inlineStr">
@@ -9191,22 +9167,22 @@
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001175</t>
+          <t>ARI:0001176</t>
         </is>
       </c>
       <c r="B175" s="3" t="inlineStr">
         <is>
-          <t>Rasmussen syndrome</t>
+          <t>Secondary Raynaud's phenomenon</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>230191005</t>
+          <t>356198000</t>
         </is>
       </c>
       <c r="D175" s="3" t="inlineStr">
         <is>
-          <t>Rasmussen syndrome</t>
+          <t>Secondary Raynaud's phenomenon</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
@@ -9226,13 +9202,13 @@
       </c>
       <c r="H175" s="4" t="inlineStr">
         <is>
-          <t>4041672</t>
+          <t>4229162</t>
         </is>
       </c>
       <c r="I175" s="2" t="inlineStr"/>
       <c r="J175" s="3" t="inlineStr">
         <is>
-          <t>230191005, 435341000124104</t>
+          <t>356198000, 266261006</t>
         </is>
       </c>
       <c r="K175" s="5" t="inlineStr">
@@ -9244,22 +9220,22 @@
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001176</t>
+          <t>ARI:0001177</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
         <is>
-          <t>Secondary Raynaud's phenomenon</t>
+          <t>Reactive arthritis</t>
         </is>
       </c>
       <c r="C176" s="4" t="inlineStr">
         <is>
-          <t>356198000</t>
+          <t>201736002</t>
         </is>
       </c>
       <c r="D176" s="3" t="inlineStr">
         <is>
-          <t>Secondary Raynaud's phenomenon</t>
+          <t>Reactive arthritis</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
@@ -9279,13 +9255,13 @@
       </c>
       <c r="H176" s="4" t="inlineStr">
         <is>
-          <t>4229162</t>
+          <t>40399768</t>
         </is>
       </c>
       <c r="I176" s="2" t="inlineStr"/>
       <c r="J176" s="3" t="inlineStr">
         <is>
-          <t>356198000, 266261006</t>
+          <t>201736002, 67224007</t>
         </is>
       </c>
       <c r="K176" s="5" t="inlineStr">
@@ -9297,22 +9273,22 @@
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001177</t>
+          <t>ARI:0001178</t>
         </is>
       </c>
       <c r="B177" s="3" t="inlineStr">
         <is>
-          <t>Reactive arthritis</t>
+          <t>Relapsing polychondritis</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>201736002</t>
+          <t>72275000</t>
         </is>
       </c>
       <c r="D177" s="3" t="inlineStr">
         <is>
-          <t>Reactive arthritis</t>
+          <t>Relapsing polychondritis</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
@@ -9332,13 +9308,13 @@
       </c>
       <c r="H177" s="4" t="inlineStr">
         <is>
-          <t>40399768</t>
+          <t>4216873</t>
         </is>
       </c>
       <c r="I177" s="2" t="inlineStr"/>
       <c r="J177" s="3" t="inlineStr">
         <is>
-          <t>201736002, 67224007</t>
+          <t>72275000</t>
         </is>
       </c>
       <c r="K177" s="5" t="inlineStr">
@@ -9350,22 +9326,22 @@
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001178</t>
+          <t>ARI:0001179</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
         <is>
-          <t>Relapsing polychondritis</t>
+          <t>Restless legs</t>
         </is>
       </c>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>72275000</t>
+          <t>32914008</t>
         </is>
       </c>
       <c r="D178" s="3" t="inlineStr">
         <is>
-          <t>Relapsing polychondritis</t>
+          <t>Restless legs</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
@@ -9385,13 +9361,13 @@
       </c>
       <c r="H178" s="4" t="inlineStr">
         <is>
-          <t>4216873</t>
+          <t>73754</t>
         </is>
       </c>
       <c r="I178" s="2" t="inlineStr"/>
       <c r="J178" s="3" t="inlineStr">
         <is>
-          <t>72275000</t>
+          <t>32914008</t>
         </is>
       </c>
       <c r="K178" s="5" t="inlineStr">
@@ -9403,22 +9379,22 @@
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001179</t>
+          <t>ARI:0001180</t>
         </is>
       </c>
       <c r="B179" s="3" t="inlineStr">
         <is>
-          <t>Restless legs</t>
+          <t>Retinocochleocerebral vasculopathy</t>
         </is>
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>32914008</t>
+          <t>702575003</t>
         </is>
       </c>
       <c r="D179" s="3" t="inlineStr">
         <is>
-          <t>Restless legs</t>
+          <t>Retinocochleocerebral vasculopathy</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
@@ -9438,13 +9414,13 @@
       </c>
       <c r="H179" s="4" t="inlineStr">
         <is>
-          <t>73754</t>
+          <t>45765600</t>
         </is>
       </c>
       <c r="I179" s="2" t="inlineStr"/>
       <c r="J179" s="3" t="inlineStr">
         <is>
-          <t>32914008</t>
+          <t>702575003</t>
         </is>
       </c>
       <c r="K179" s="5" t="inlineStr">
@@ -9456,27 +9432,27 @@
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001180</t>
+          <t>ARI:0001181</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
         <is>
-          <t>Retinocochleocerebral vasculopathy</t>
+          <t>Rheumatic Chorea</t>
         </is>
       </c>
       <c r="C180" s="4" t="inlineStr">
         <is>
-          <t>702575003</t>
+          <t>46826000</t>
         </is>
       </c>
       <c r="D180" s="3" t="inlineStr">
         <is>
-          <t>Retinocochleocerebral vasculopathy</t>
+          <t>Rheumatic chorea</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>0.778</t>
+          <t>0.772</t>
         </is>
       </c>
       <c r="F180" s="2" t="inlineStr">
@@ -9491,13 +9467,13 @@
       </c>
       <c r="H180" s="4" t="inlineStr">
         <is>
-          <t>45765600</t>
+          <t>444120</t>
         </is>
       </c>
       <c r="I180" s="2" t="inlineStr"/>
       <c r="J180" s="3" t="inlineStr">
         <is>
-          <t>702575003</t>
+          <t>46826000</t>
         </is>
       </c>
       <c r="K180" s="5" t="inlineStr">
@@ -9509,27 +9485,27 @@
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001181</t>
+          <t>ARI:0001182</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr">
         <is>
-          <t>Rheumatic Chorea</t>
+          <t>Rheumatic fever</t>
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>46826000</t>
+          <t>58718002</t>
         </is>
       </c>
       <c r="D181" s="3" t="inlineStr">
         <is>
-          <t>Rheumatic chorea</t>
+          <t>Rheumatic fever</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>0.772</t>
+          <t>0.778</t>
         </is>
       </c>
       <c r="F181" s="2" t="inlineStr">
@@ -9544,13 +9520,13 @@
       </c>
       <c r="H181" s="4" t="inlineStr">
         <is>
-          <t>444120</t>
+          <t>442313</t>
         </is>
       </c>
       <c r="I181" s="2" t="inlineStr"/>
       <c r="J181" s="3" t="inlineStr">
         <is>
-          <t>46826000</t>
+          <t>194709000, 58718002</t>
         </is>
       </c>
       <c r="K181" s="5" t="inlineStr">
@@ -9562,22 +9538,22 @@
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001182</t>
+          <t>ARI:0001183</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
         <is>
-          <t>Rheumatic fever</t>
+          <t>Rheumatoid aortitis</t>
         </is>
       </c>
       <c r="C182" s="4" t="inlineStr">
         <is>
-          <t>58718002</t>
+          <t>38877003</t>
         </is>
       </c>
       <c r="D182" s="3" t="inlineStr">
         <is>
-          <t>Rheumatic fever</t>
+          <t>Rheumatoid aortitis</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
@@ -9597,13 +9573,13 @@
       </c>
       <c r="H182" s="4" t="inlineStr">
         <is>
-          <t>442313</t>
+          <t>4306357</t>
         </is>
       </c>
       <c r="I182" s="2" t="inlineStr"/>
       <c r="J182" s="3" t="inlineStr">
         <is>
-          <t>58718002, 194709000</t>
+          <t>38877003</t>
         </is>
       </c>
       <c r="K182" s="5" t="inlineStr">
@@ -9615,22 +9591,22 @@
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001183</t>
+          <t>ARI:0001184</t>
         </is>
       </c>
       <c r="B183" s="3" t="inlineStr">
         <is>
-          <t>Rheumatoid aortitis</t>
+          <t>Rheumatoid arthritis</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>38877003</t>
+          <t>69896004</t>
         </is>
       </c>
       <c r="D183" s="3" t="inlineStr">
         <is>
-          <t>Rheumatoid aortitis</t>
+          <t>Rheumatoid arthritis</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
@@ -9650,13 +9626,13 @@
       </c>
       <c r="H183" s="4" t="inlineStr">
         <is>
-          <t>4306357</t>
+          <t>80809</t>
         </is>
       </c>
       <c r="I183" s="2" t="inlineStr"/>
       <c r="J183" s="3" t="inlineStr">
         <is>
-          <t>38877003</t>
+          <t>69896004</t>
         </is>
       </c>
       <c r="K183" s="5" t="inlineStr">
@@ -9668,22 +9644,22 @@
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001184</t>
+          <t>ARI:0001185</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
         <is>
-          <t>Rheumatoid arthritis</t>
+          <t>Rheumatoid vasculitis</t>
         </is>
       </c>
       <c r="C184" s="4" t="inlineStr">
         <is>
-          <t>69896004</t>
+          <t>400054000</t>
         </is>
       </c>
       <c r="D184" s="3" t="inlineStr">
         <is>
-          <t>Rheumatoid arthritis</t>
+          <t>Rheumatoid vasculitis</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
@@ -9703,13 +9679,13 @@
       </c>
       <c r="H184" s="4" t="inlineStr">
         <is>
-          <t>80809</t>
+          <t>4271003</t>
         </is>
       </c>
       <c r="I184" s="2" t="inlineStr"/>
       <c r="J184" s="3" t="inlineStr">
         <is>
-          <t>69896004</t>
+          <t>400054000</t>
         </is>
       </c>
       <c r="K184" s="5" t="inlineStr">
@@ -9721,22 +9697,22 @@
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001185</t>
+          <t>ARI:0001186</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
         <is>
-          <t>Rheumatoid vasculitis</t>
+          <t>Sarcoidosis</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t>400054000</t>
+          <t>31541009</t>
         </is>
       </c>
       <c r="D185" s="3" t="inlineStr">
         <is>
-          <t>Rheumatoid vasculitis</t>
+          <t>Sarcoidosis</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
@@ -9756,13 +9732,13 @@
       </c>
       <c r="H185" s="4" t="inlineStr">
         <is>
-          <t>4271003</t>
+          <t>438688</t>
         </is>
       </c>
       <c r="I185" s="2" t="inlineStr"/>
       <c r="J185" s="3" t="inlineStr">
         <is>
-          <t>400054000</t>
+          <t>31541009, 238676008, 72470008</t>
         </is>
       </c>
       <c r="K185" s="5" t="inlineStr">
@@ -9774,22 +9750,22 @@
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001186</t>
+          <t>ARI:0001187</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
         <is>
-          <t>Sarcoidosis</t>
+          <t>Schnitzler syndrome</t>
         </is>
       </c>
       <c r="C186" s="4" t="inlineStr">
         <is>
-          <t>31541009</t>
+          <t>402415001</t>
         </is>
       </c>
       <c r="D186" s="3" t="inlineStr">
         <is>
-          <t>Sarcoidosis</t>
+          <t>Schnitzler syndrome</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
@@ -9809,13 +9785,13 @@
       </c>
       <c r="H186" s="4" t="inlineStr">
         <is>
-          <t>438688</t>
+          <t>4297647</t>
         </is>
       </c>
       <c r="I186" s="2" t="inlineStr"/>
       <c r="J186" s="3" t="inlineStr">
         <is>
-          <t>72470008, 238676008, 31541009</t>
+          <t>402415001</t>
         </is>
       </c>
       <c r="K186" s="5" t="inlineStr">
@@ -9827,22 +9803,22 @@
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001187</t>
+          <t>ARI:0001188</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
         <is>
-          <t>Schnitzler syndrome</t>
+          <t>Scleritis</t>
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>402415001</t>
+          <t>78370002</t>
         </is>
       </c>
       <c r="D187" s="3" t="inlineStr">
         <is>
-          <t>Schnitzler syndrome</t>
+          <t>Scleritis</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
@@ -9862,13 +9838,13 @@
       </c>
       <c r="H187" s="4" t="inlineStr">
         <is>
-          <t>4297647</t>
+          <t>434944</t>
         </is>
       </c>
       <c r="I187" s="2" t="inlineStr"/>
       <c r="J187" s="3" t="inlineStr">
         <is>
-          <t>402415001</t>
+          <t>78370002</t>
         </is>
       </c>
       <c r="K187" s="5" t="inlineStr">
@@ -9880,22 +9856,22 @@
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001188</t>
+          <t>ARI:0001189</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
         <is>
-          <t>Scleritis</t>
+          <t>Sjögren's disease</t>
         </is>
       </c>
       <c r="C188" s="4" t="inlineStr">
         <is>
-          <t>78370002</t>
+          <t>83901003</t>
         </is>
       </c>
       <c r="D188" s="3" t="inlineStr">
         <is>
-          <t>Scleritis</t>
+          <t>Sjögren's syndrome</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
@@ -9910,18 +9886,18 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>(preferred name)</t>
+          <t>Sjögren's syndrome</t>
         </is>
       </c>
       <c r="H188" s="4" t="inlineStr">
         <is>
-          <t>434944</t>
+          <t>254443</t>
         </is>
       </c>
       <c r="I188" s="2" t="inlineStr"/>
       <c r="J188" s="3" t="inlineStr">
         <is>
-          <t>78370002</t>
+          <t>83901003</t>
         </is>
       </c>
       <c r="K188" s="5" t="inlineStr">
@@ -9933,22 +9909,22 @@
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001189</t>
+          <t>ARI:0001190</t>
         </is>
       </c>
       <c r="B189" s="3" t="inlineStr">
         <is>
-          <t>Sjögren's disease</t>
+          <t>SLE glomerulonephritis syndrome</t>
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t>302896008</t>
+          <t>68815009</t>
         </is>
       </c>
       <c r="D189" s="3" t="inlineStr">
         <is>
-          <t>Keratoconjunctivitis sicca</t>
+          <t>SLE glomerulonephritis syndrome</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
@@ -9963,41 +9939,45 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>Keratoconjunctivitis sicca</t>
+          <t>(preferred name)</t>
         </is>
       </c>
       <c r="H189" s="4" t="inlineStr">
         <is>
-          <t>4120320</t>
+          <t>4285717</t>
         </is>
       </c>
       <c r="I189" s="2" t="inlineStr"/>
       <c r="J189" s="3" t="inlineStr">
         <is>
-          <t>83901003</t>
-        </is>
-      </c>
-      <c r="K189" s="2" t="inlineStr"/>
+          <t>68815009</t>
+        </is>
+      </c>
+      <c r="K189" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001190</t>
+          <t>ARI:0001191</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
         <is>
-          <t>SLE glomerulonephritis syndrome</t>
+          <t>Small fiber neuropathy</t>
         </is>
       </c>
       <c r="C190" s="4" t="inlineStr">
         <is>
-          <t>68815009</t>
+          <t>709489006</t>
         </is>
       </c>
       <c r="D190" s="3" t="inlineStr">
         <is>
-          <t>SLE glomerulonephritis syndrome</t>
+          <t>Small fiber neuropathy</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
@@ -10017,13 +9997,13 @@
       </c>
       <c r="H190" s="4" t="inlineStr">
         <is>
-          <t>4285717</t>
+          <t>46271378</t>
         </is>
       </c>
       <c r="I190" s="2" t="inlineStr"/>
       <c r="J190" s="3" t="inlineStr">
         <is>
-          <t>68815009</t>
+          <t>709489006</t>
         </is>
       </c>
       <c r="K190" s="5" t="inlineStr">
@@ -10035,22 +10015,22 @@
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001191</t>
+          <t>ARI:0001192</t>
         </is>
       </c>
       <c r="B191" s="3" t="inlineStr">
         <is>
-          <t>Small fiber neuropathy</t>
+          <t>Steroid-responsive encephalopathy associated with autoimmune thyroiditis</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>709489006</t>
+          <t>771271000</t>
         </is>
       </c>
       <c r="D191" s="3" t="inlineStr">
         <is>
-          <t>Small fiber neuropathy</t>
+          <t>Steroid-responsive encephalopathy associated with autoimmune thyroiditis</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
@@ -10070,13 +10050,13 @@
       </c>
       <c r="H191" s="4" t="inlineStr">
         <is>
-          <t>46271378</t>
+          <t>36674282</t>
         </is>
       </c>
       <c r="I191" s="2" t="inlineStr"/>
       <c r="J191" s="3" t="inlineStr">
         <is>
-          <t>709489006</t>
+          <t>771271000</t>
         </is>
       </c>
       <c r="K191" s="5" t="inlineStr">
@@ -10088,22 +10068,22 @@
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001192</t>
+          <t>ARI:0001193</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
         <is>
-          <t>Steroid-responsive encephalopathy associated with autoimmune thyroiditis</t>
+          <t>Stiff-person syndrome</t>
         </is>
       </c>
       <c r="C192" s="4" t="inlineStr">
         <is>
-          <t>771271000</t>
+          <t>5217008</t>
         </is>
       </c>
       <c r="D192" s="3" t="inlineStr">
         <is>
-          <t>Steroid-responsive encephalopathy associated with autoimmune thyroiditis</t>
+          <t>Stiff-person syndrome</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
@@ -10123,13 +10103,13 @@
       </c>
       <c r="H192" s="4" t="inlineStr">
         <is>
-          <t>36674282</t>
+          <t>379008</t>
         </is>
       </c>
       <c r="I192" s="2" t="inlineStr"/>
       <c r="J192" s="3" t="inlineStr">
         <is>
-          <t>771271000</t>
+          <t>5217008</t>
         </is>
       </c>
       <c r="K192" s="5" t="inlineStr">
@@ -10141,22 +10121,22 @@
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001193</t>
+          <t>ARI:0001194</t>
         </is>
       </c>
       <c r="B193" s="3" t="inlineStr">
         <is>
-          <t>Stiff-person syndrome</t>
+          <t>Subacute bacterial endocarditis</t>
         </is>
       </c>
       <c r="C193" s="4" t="inlineStr">
         <is>
-          <t>5217008</t>
+          <t>73774007</t>
         </is>
       </c>
       <c r="D193" s="3" t="inlineStr">
         <is>
-          <t>Stiff-person syndrome</t>
+          <t>Subacute bacterial endocarditis</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
@@ -10176,13 +10156,13 @@
       </c>
       <c r="H193" s="4" t="inlineStr">
         <is>
-          <t>379008</t>
+          <t>4249899</t>
         </is>
       </c>
       <c r="I193" s="2" t="inlineStr"/>
       <c r="J193" s="3" t="inlineStr">
         <is>
-          <t>5217008</t>
+          <t>73774007</t>
         </is>
       </c>
       <c r="K193" s="5" t="inlineStr">
@@ -10194,22 +10174,22 @@
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001194</t>
+          <t>ARI:0001195</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
         <is>
-          <t>Subacute bacterial endocarditis</t>
+          <t>Sympathetic uveitis</t>
         </is>
       </c>
       <c r="C194" s="4" t="inlineStr">
         <is>
-          <t>73774007</t>
+          <t>75315001</t>
         </is>
       </c>
       <c r="D194" s="3" t="inlineStr">
         <is>
-          <t>Subacute bacterial endocarditis</t>
+          <t>Sympathetic uveitis</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
@@ -10229,13 +10209,13 @@
       </c>
       <c r="H194" s="4" t="inlineStr">
         <is>
-          <t>4249899</t>
+          <t>438739</t>
         </is>
       </c>
       <c r="I194" s="2" t="inlineStr"/>
       <c r="J194" s="3" t="inlineStr">
         <is>
-          <t>73774007</t>
+          <t>75315001</t>
         </is>
       </c>
       <c r="K194" s="5" t="inlineStr">
@@ -10247,22 +10227,22 @@
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001195</t>
+          <t>ARI:0001196</t>
         </is>
       </c>
       <c r="B195" s="3" t="inlineStr">
         <is>
-          <t>Sympathetic uveitis</t>
+          <t>Systemic lupus erythematosus</t>
         </is>
       </c>
       <c r="C195" s="4" t="inlineStr">
         <is>
-          <t>75315001</t>
+          <t>55464009</t>
         </is>
       </c>
       <c r="D195" s="3" t="inlineStr">
         <is>
-          <t>Sympathetic uveitis</t>
+          <t>Systemic lupus erythematosus</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
@@ -10282,13 +10262,13 @@
       </c>
       <c r="H195" s="4" t="inlineStr">
         <is>
-          <t>438739</t>
+          <t>257628</t>
         </is>
       </c>
       <c r="I195" s="2" t="inlineStr"/>
       <c r="J195" s="3" t="inlineStr">
         <is>
-          <t>75315001</t>
+          <t>55464009</t>
         </is>
       </c>
       <c r="K195" s="5" t="inlineStr">
@@ -10300,22 +10280,22 @@
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001196</t>
+          <t>ARI:0001197</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
         <is>
-          <t>Systemic lupus erythematosus</t>
+          <t>Systemic mast cell disease</t>
         </is>
       </c>
       <c r="C196" s="4" t="inlineStr">
         <is>
-          <t>55464009</t>
+          <t>397016004</t>
         </is>
       </c>
       <c r="D196" s="3" t="inlineStr">
         <is>
-          <t>Systemic lupus erythematosus</t>
+          <t>Systemic mast cell disease</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
@@ -10335,13 +10315,13 @@
       </c>
       <c r="H196" s="4" t="inlineStr">
         <is>
-          <t>257628</t>
+          <t>4246284</t>
         </is>
       </c>
       <c r="I196" s="2" t="inlineStr"/>
       <c r="J196" s="3" t="inlineStr">
         <is>
-          <t>55464009</t>
+          <t>397016004</t>
         </is>
       </c>
       <c r="K196" s="5" t="inlineStr">
@@ -10353,22 +10333,22 @@
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001197</t>
+          <t>ARI:0001198</t>
         </is>
       </c>
       <c r="B197" s="3" t="inlineStr">
         <is>
-          <t>Systemic mast cell disease</t>
+          <t>Systemic sclerosis</t>
         </is>
       </c>
       <c r="C197" s="4" t="inlineStr">
         <is>
-          <t>397016004</t>
+          <t>89155008</t>
         </is>
       </c>
       <c r="D197" s="3" t="inlineStr">
         <is>
-          <t>Systemic mast cell disease</t>
+          <t>Systemic sclerosis</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
@@ -10388,13 +10368,13 @@
       </c>
       <c r="H197" s="4" t="inlineStr">
         <is>
-          <t>4246284</t>
+          <t>134442</t>
         </is>
       </c>
       <c r="I197" s="2" t="inlineStr"/>
       <c r="J197" s="3" t="inlineStr">
         <is>
-          <t>397016004</t>
+          <t>89155008</t>
         </is>
       </c>
       <c r="K197" s="5" t="inlineStr">
@@ -10406,22 +10386,22 @@
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001198</t>
+          <t>ARI:0001199</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
         <is>
-          <t>Systemic sclerosis</t>
+          <t>Systemic sclerosis with limited cutaneous involvement</t>
         </is>
       </c>
       <c r="C198" s="4" t="inlineStr">
         <is>
-          <t>89155008</t>
+          <t>298285004</t>
         </is>
       </c>
       <c r="D198" s="3" t="inlineStr">
         <is>
-          <t>Systemic sclerosis</t>
+          <t>Systemic sclerosis with limited cutaneous involvement</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
@@ -10441,13 +10421,13 @@
       </c>
       <c r="H198" s="4" t="inlineStr">
         <is>
-          <t>134442</t>
+          <t>4185187</t>
         </is>
       </c>
       <c r="I198" s="2" t="inlineStr"/>
       <c r="J198" s="3" t="inlineStr">
         <is>
-          <t>89155008</t>
+          <t>298285004</t>
         </is>
       </c>
       <c r="K198" s="5" t="inlineStr">
@@ -10459,22 +10439,22 @@
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001199</t>
+          <t>ARI:0001200</t>
         </is>
       </c>
       <c r="B199" s="3" t="inlineStr">
         <is>
-          <t>Systemic sclerosis with limited cutaneous involvement</t>
+          <t>Takayasu's arteritis</t>
         </is>
       </c>
       <c r="C199" s="4" t="inlineStr">
         <is>
-          <t>298285004</t>
+          <t>359789008</t>
         </is>
       </c>
       <c r="D199" s="3" t="inlineStr">
         <is>
-          <t>Systemic sclerosis with limited cutaneous involvement</t>
+          <t>Takayasu's disease</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
@@ -10489,18 +10469,18 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>(preferred name)</t>
+          <t>Takayasu's disease</t>
         </is>
       </c>
       <c r="H199" s="4" t="inlineStr">
         <is>
-          <t>4185187</t>
+          <t>440740</t>
         </is>
       </c>
       <c r="I199" s="2" t="inlineStr"/>
       <c r="J199" s="3" t="inlineStr">
         <is>
-          <t>298285004, 31848007, 128461001</t>
+          <t>359789008</t>
         </is>
       </c>
       <c r="K199" s="5" t="inlineStr">
@@ -10512,22 +10492,22 @@
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001200</t>
+          <t>ARI:0001201</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
         <is>
-          <t>Takayasu's arteritis</t>
+          <t>Temporal arteritis</t>
         </is>
       </c>
       <c r="C200" s="4" t="inlineStr">
         <is>
-          <t>359789008</t>
+          <t>400130008</t>
         </is>
       </c>
       <c r="D200" s="3" t="inlineStr">
         <is>
-          <t>Takayasu's disease</t>
+          <t>Temporal arteritis</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
@@ -10542,18 +10522,18 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>Takayasu's disease</t>
+          <t>(preferred name)</t>
         </is>
       </c>
       <c r="H200" s="4" t="inlineStr">
         <is>
-          <t>440740</t>
+          <t>4290976</t>
         </is>
       </c>
       <c r="I200" s="2" t="inlineStr"/>
       <c r="J200" s="3" t="inlineStr">
         <is>
-          <t>359789008</t>
+          <t>400130008</t>
         </is>
       </c>
       <c r="K200" s="5" t="inlineStr">
@@ -10565,110 +10545,110 @@
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001201</t>
+          <t>ARI:0001202</t>
         </is>
       </c>
       <c r="B201" s="3" t="inlineStr">
         <is>
-          <t>Temporal arteritis</t>
-        </is>
-      </c>
-      <c r="C201" s="4" t="inlineStr">
-        <is>
-          <t>400130008</t>
-        </is>
-      </c>
-      <c r="D201" s="3" t="inlineStr">
-        <is>
-          <t>Temporal arteritis</t>
-        </is>
-      </c>
-      <c r="E201" s="2" t="inlineStr">
-        <is>
-          <t>0.778</t>
-        </is>
-      </c>
-      <c r="F201" s="2" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
+          <t>TIF1-gamma positive dermatomyositis</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr"/>
+      <c r="D201" s="3" t="inlineStr"/>
+      <c r="E201" s="2" t="inlineStr"/>
+      <c r="F201" s="2" t="inlineStr"/>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>(preferred name)</t>
-        </is>
-      </c>
-      <c r="H201" s="4" t="inlineStr">
-        <is>
-          <t>4290976</t>
-        </is>
-      </c>
+          <t>no match</t>
+        </is>
+      </c>
+      <c r="H201" s="2" t="inlineStr"/>
       <c r="I201" s="2" t="inlineStr"/>
-      <c r="J201" s="3" t="inlineStr">
-        <is>
-          <t>400130008</t>
-        </is>
-      </c>
-      <c r="K201" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="J201" s="3" t="inlineStr"/>
+      <c r="K201" s="2" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001202</t>
+          <t>ARI:0001203</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
         <is>
-          <t>TIF1-gamma positive dermatomyositis</t>
-        </is>
-      </c>
-      <c r="C202" s="2" t="inlineStr"/>
-      <c r="D202" s="3" t="inlineStr"/>
-      <c r="E202" s="2" t="inlineStr"/>
-      <c r="F202" s="2" t="inlineStr"/>
+          <t>Tolosa-Hunt syndrome</t>
+        </is>
+      </c>
+      <c r="C202" s="4" t="inlineStr">
+        <is>
+          <t>95794005</t>
+        </is>
+      </c>
+      <c r="D202" s="3" t="inlineStr">
+        <is>
+          <t>Tolosa-Hunt syndrome</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="inlineStr">
+        <is>
+          <t>0.778</t>
+        </is>
+      </c>
+      <c r="F202" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>no match</t>
-        </is>
-      </c>
-      <c r="H202" s="2" t="inlineStr"/>
+          <t>(preferred name)</t>
+        </is>
+      </c>
+      <c r="H202" s="4" t="inlineStr">
+        <is>
+          <t>4317989</t>
+        </is>
+      </c>
       <c r="I202" s="2" t="inlineStr"/>
-      <c r="J202" s="3" t="inlineStr"/>
-      <c r="K202" s="2" t="inlineStr"/>
+      <c r="J202" s="3" t="inlineStr">
+        <is>
+          <t>95794005</t>
+        </is>
+      </c>
+      <c r="K202" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001203</t>
+          <t>ARI:0001204</t>
         </is>
       </c>
       <c r="B203" s="3" t="inlineStr">
         <is>
-          <t>Tolosa-Hunt syndrome</t>
+          <t>Transverse myelitis</t>
         </is>
       </c>
       <c r="C203" s="4" t="inlineStr">
         <is>
-          <t>95794005</t>
+          <t>16631009</t>
         </is>
       </c>
       <c r="D203" s="3" t="inlineStr">
         <is>
-          <t>Tolosa-Hunt syndrome</t>
+          <t>Transverse myelopathy syndrome</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>0.778</t>
+          <t>0.556</t>
         </is>
       </c>
       <c r="F203" s="2" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>synonym</t>
         </is>
       </c>
       <c r="G203" s="3" t="inlineStr">
@@ -10678,13 +10658,13 @@
       </c>
       <c r="H203" s="4" t="inlineStr">
         <is>
-          <t>4317989</t>
+          <t>443904</t>
         </is>
       </c>
       <c r="I203" s="2" t="inlineStr"/>
       <c r="J203" s="3" t="inlineStr">
         <is>
-          <t>95794005</t>
+          <t>16631009</t>
         </is>
       </c>
       <c r="K203" s="5" t="inlineStr">
@@ -10696,32 +10676,32 @@
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001204</t>
+          <t>ARI:0001205</t>
         </is>
       </c>
       <c r="B204" s="3" t="inlineStr">
         <is>
-          <t>Transverse myelitis</t>
+          <t>Ulcerative colitis</t>
         </is>
       </c>
       <c r="C204" s="4" t="inlineStr">
         <is>
-          <t>16631009</t>
+          <t>64766004</t>
         </is>
       </c>
       <c r="D204" s="3" t="inlineStr">
         <is>
-          <t>Transverse myelopathy syndrome</t>
+          <t>Ulcerative colitis</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>0.556</t>
+          <t>0.778</t>
         </is>
       </c>
       <c r="F204" s="2" t="inlineStr">
         <is>
-          <t>synonym</t>
+          <t>name</t>
         </is>
       </c>
       <c r="G204" s="3" t="inlineStr">
@@ -10731,13 +10711,13 @@
       </c>
       <c r="H204" s="4" t="inlineStr">
         <is>
-          <t>443904</t>
+          <t>81893</t>
         </is>
       </c>
       <c r="I204" s="2" t="inlineStr"/>
       <c r="J204" s="3" t="inlineStr">
         <is>
-          <t>16631009</t>
+          <t>64766004</t>
         </is>
       </c>
       <c r="K204" s="5" t="inlineStr">
@@ -10749,22 +10729,22 @@
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001205</t>
+          <t>ARI:0001206</t>
         </is>
       </c>
       <c r="B205" s="3" t="inlineStr">
         <is>
-          <t>Ulcerative colitis</t>
+          <t>Undifferentiated connective tissue disease</t>
         </is>
       </c>
       <c r="C205" s="4" t="inlineStr">
         <is>
-          <t>64766004</t>
+          <t>239918008</t>
         </is>
       </c>
       <c r="D205" s="3" t="inlineStr">
         <is>
-          <t>Ulcerative colitis</t>
+          <t>Undifferentiated connective tissue disease</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr">
@@ -10784,13 +10764,13 @@
       </c>
       <c r="H205" s="4" t="inlineStr">
         <is>
-          <t>81893</t>
+          <t>4344165</t>
         </is>
       </c>
       <c r="I205" s="2" t="inlineStr"/>
       <c r="J205" s="3" t="inlineStr">
         <is>
-          <t>64766004</t>
+          <t>239918008</t>
         </is>
       </c>
       <c r="K205" s="5" t="inlineStr">
@@ -10802,104 +10782,104 @@
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001206</t>
+          <t>ARI:0001207</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
         <is>
-          <t>Undifferentiated connective tissue disease</t>
-        </is>
-      </c>
-      <c r="C206" s="4" t="inlineStr">
-        <is>
-          <t>239918008</t>
-        </is>
-      </c>
-      <c r="D206" s="3" t="inlineStr">
-        <is>
-          <t>Undifferentiated connective tissue disease</t>
-        </is>
-      </c>
-      <c r="E206" s="2" t="inlineStr">
-        <is>
-          <t>0.778</t>
-        </is>
-      </c>
-      <c r="F206" s="2" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
+          <t>Urticarial vasculitis</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="inlineStr"/>
+      <c r="D206" s="3" t="inlineStr"/>
+      <c r="E206" s="2" t="inlineStr"/>
+      <c r="F206" s="2" t="inlineStr"/>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>(preferred name)</t>
-        </is>
-      </c>
-      <c r="H206" s="4" t="inlineStr">
-        <is>
-          <t>4344165</t>
-        </is>
-      </c>
+          <t>no match</t>
+        </is>
+      </c>
+      <c r="H206" s="2" t="inlineStr"/>
       <c r="I206" s="2" t="inlineStr"/>
       <c r="J206" s="3" t="inlineStr">
         <is>
-          <t>239918008</t>
-        </is>
-      </c>
-      <c r="K206" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>402656007</t>
+        </is>
+      </c>
+      <c r="K206" s="2" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001207</t>
+          <t>ARI:0001208</t>
         </is>
       </c>
       <c r="B207" s="3" t="inlineStr">
         <is>
-          <t>Urticarial vasculitis</t>
-        </is>
-      </c>
-      <c r="C207" s="2" t="inlineStr"/>
-      <c r="D207" s="3" t="inlineStr"/>
-      <c r="E207" s="2" t="inlineStr"/>
-      <c r="F207" s="2" t="inlineStr"/>
+          <t>Uveitis</t>
+        </is>
+      </c>
+      <c r="C207" s="4" t="inlineStr">
+        <is>
+          <t>128473001</t>
+        </is>
+      </c>
+      <c r="D207" s="3" t="inlineStr">
+        <is>
+          <t>Uveitis</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="inlineStr">
+        <is>
+          <t>0.778</t>
+        </is>
+      </c>
+      <c r="F207" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>no match</t>
-        </is>
-      </c>
-      <c r="H207" s="2" t="inlineStr"/>
+          <t>(preferred name)</t>
+        </is>
+      </c>
+      <c r="H207" s="4" t="inlineStr">
+        <is>
+          <t>4028363</t>
+        </is>
+      </c>
       <c r="I207" s="2" t="inlineStr"/>
       <c r="J207" s="3" t="inlineStr">
         <is>
-          <t>402656007</t>
-        </is>
-      </c>
-      <c r="K207" s="2" t="inlineStr"/>
+          <t>128473001</t>
+        </is>
+      </c>
+      <c r="K207" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001208</t>
+          <t>ARI:0001209</t>
         </is>
       </c>
       <c r="B208" s="3" t="inlineStr">
         <is>
-          <t>Uveitis</t>
+          <t>Vitiligo</t>
         </is>
       </c>
       <c r="C208" s="4" t="inlineStr">
         <is>
-          <t>128473001</t>
+          <t>56727007</t>
         </is>
       </c>
       <c r="D208" s="3" t="inlineStr">
         <is>
-          <t>Uveitis</t>
+          <t>Vitiligo</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
@@ -10919,13 +10899,13 @@
       </c>
       <c r="H208" s="4" t="inlineStr">
         <is>
-          <t>4028363</t>
+          <t>138502</t>
         </is>
       </c>
       <c r="I208" s="2" t="inlineStr"/>
       <c r="J208" s="3" t="inlineStr">
         <is>
-          <t>128473001, 231947004</t>
+          <t>56727007</t>
         </is>
       </c>
       <c r="K208" s="5" t="inlineStr">
@@ -10937,22 +10917,22 @@
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001209</t>
+          <t>ARI:0001210</t>
         </is>
       </c>
       <c r="B209" s="3" t="inlineStr">
         <is>
-          <t>Vitiligo</t>
+          <t>Vogt-Koyanagi-Harada disease</t>
         </is>
       </c>
       <c r="C209" s="4" t="inlineStr">
         <is>
-          <t>56727007</t>
+          <t>193497004</t>
         </is>
       </c>
       <c r="D209" s="3" t="inlineStr">
         <is>
-          <t>Vitiligo</t>
+          <t>Vogt-Koyanagi-Harada disease</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
@@ -10972,13 +10952,13 @@
       </c>
       <c r="H209" s="4" t="inlineStr">
         <is>
-          <t>138502</t>
+          <t>4108968</t>
         </is>
       </c>
       <c r="I209" s="2" t="inlineStr"/>
       <c r="J209" s="3" t="inlineStr">
         <is>
-          <t>56727007</t>
+          <t>193497004</t>
         </is>
       </c>
       <c r="K209" s="5" t="inlineStr">
@@ -10990,22 +10970,22 @@
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001210</t>
+          <t>ARI:0001211</t>
         </is>
       </c>
       <c r="B210" s="3" t="inlineStr">
         <is>
-          <t>Vogt-Koyanagi-Harada disease</t>
+          <t>Warm autoimmune hemolytic anemia</t>
         </is>
       </c>
       <c r="C210" s="4" t="inlineStr">
         <is>
-          <t>193497004</t>
+          <t>3978000</t>
         </is>
       </c>
       <c r="D210" s="3" t="inlineStr">
         <is>
-          <t>Vogt-Koyanagi-Harada disease</t>
+          <t>Warm autoimmune hemolytic anemia</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
@@ -11025,13 +11005,13 @@
       </c>
       <c r="H210" s="4" t="inlineStr">
         <is>
-          <t>4108968</t>
+          <t>4219853</t>
         </is>
       </c>
       <c r="I210" s="2" t="inlineStr"/>
       <c r="J210" s="3" t="inlineStr">
         <is>
-          <t>193497004</t>
+          <t>3978000</t>
         </is>
       </c>
       <c r="K210" s="5" t="inlineStr">
@@ -11043,27 +11023,27 @@
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001211</t>
+          <t>ARI:0001212</t>
         </is>
       </c>
       <c r="B211" s="3" t="inlineStr">
         <is>
-          <t>Warm autoimmune hemolytic anemia</t>
+          <t>CREST Syndrome</t>
         </is>
       </c>
       <c r="C211" s="4" t="inlineStr">
         <is>
-          <t>3978000</t>
+          <t>31848007</t>
         </is>
       </c>
       <c r="D211" s="3" t="inlineStr">
         <is>
-          <t>Warm autoimmune hemolytic anemia</t>
+          <t>CREST syndrome</t>
         </is>
       </c>
       <c r="E211" s="2" t="inlineStr">
         <is>
-          <t>0.778</t>
+          <t>0.772</t>
         </is>
       </c>
       <c r="F211" s="2" t="inlineStr">
@@ -11078,13 +11058,13 @@
       </c>
       <c r="H211" s="4" t="inlineStr">
         <is>
-          <t>4219853</t>
+          <t>4135937</t>
         </is>
       </c>
       <c r="I211" s="2" t="inlineStr"/>
       <c r="J211" s="3" t="inlineStr">
         <is>
-          <t>3978000</t>
+          <t>31848007</t>
         </is>
       </c>
       <c r="K211" s="5" t="inlineStr">
@@ -11092,6 +11072,113 @@
           <t>Yes</t>
         </is>
       </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>ARI:0001213</t>
+        </is>
+      </c>
+      <c r="B212" s="3" t="inlineStr">
+        <is>
+          <t>Morvan syndrome</t>
+        </is>
+      </c>
+      <c r="C212" s="4" t="inlineStr">
+        <is>
+          <t>763803004</t>
+        </is>
+      </c>
+      <c r="D212" s="3" t="inlineStr">
+        <is>
+          <t>Morvan syndrome</t>
+        </is>
+      </c>
+      <c r="E212" s="2" t="inlineStr">
+        <is>
+          <t>0.778</t>
+        </is>
+      </c>
+      <c r="F212" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="G212" s="3" t="inlineStr">
+        <is>
+          <t>(preferred name)</t>
+        </is>
+      </c>
+      <c r="H212" s="4" t="inlineStr">
+        <is>
+          <t>35622356</t>
+        </is>
+      </c>
+      <c r="I212" s="2" t="inlineStr"/>
+      <c r="J212" s="3" t="inlineStr">
+        <is>
+          <t>763803004</t>
+        </is>
+      </c>
+      <c r="K212" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>ARI:0001214</t>
+        </is>
+      </c>
+      <c r="B213" s="3" t="inlineStr">
+        <is>
+          <t>Latent autoimmune diabetes in adults (LADA)</t>
+        </is>
+      </c>
+      <c r="C213" s="2" t="inlineStr"/>
+      <c r="D213" s="3" t="inlineStr"/>
+      <c r="E213" s="2" t="inlineStr"/>
+      <c r="F213" s="2" t="inlineStr"/>
+      <c r="G213" s="3" t="inlineStr">
+        <is>
+          <t>no match</t>
+        </is>
+      </c>
+      <c r="H213" s="2" t="inlineStr"/>
+      <c r="I213" s="2" t="inlineStr"/>
+      <c r="J213" s="3" t="inlineStr">
+        <is>
+          <t>426875007</t>
+        </is>
+      </c>
+      <c r="K213" s="2" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>ARI:0001215</t>
+        </is>
+      </c>
+      <c r="B214" s="3" t="inlineStr">
+        <is>
+          <t>Fulminant type 1 diabetes</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="inlineStr"/>
+      <c r="D214" s="3" t="inlineStr"/>
+      <c r="E214" s="2" t="inlineStr"/>
+      <c r="F214" s="2" t="inlineStr"/>
+      <c r="G214" s="3" t="inlineStr">
+        <is>
+          <t>no match</t>
+        </is>
+      </c>
+      <c r="H214" s="2" t="inlineStr"/>
+      <c r="I214" s="2" t="inlineStr"/>
+      <c r="J214" s="3" t="inlineStr"/>
+      <c r="K214" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
@@ -11118,362 +11205,362 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H28" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H29" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H30" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H32" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C34" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C35" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C36" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C38" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C39" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H39" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C40" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H40" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C41" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H41" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C42" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H42" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C43" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H43" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C44" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H44" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C45" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H45" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C46" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H46" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C48" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H48" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C49" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H49" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C50" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H50" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C51" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H51" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C52" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H52" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C53" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H53" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C54" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H54" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C55" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H55" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C56" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H56" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C57" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H57" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C58" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H58" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C59" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H59" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C60" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H60" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C61" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H61" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C62" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H62" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C63" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H63" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C64" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H64" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C65" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H65" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C66" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H66" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C69" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H69" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C70" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H70" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C71" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H71" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C72" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H72" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C74" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H74" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C75" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H75" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C77" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H77" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C78" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H78" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C79" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H79" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C80" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H80" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C81" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H81" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C82" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H82" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C85" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H85" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C86" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H86" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C87" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H87" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C88" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H88" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C89" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H89" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C90" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H90" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C91" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H91" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C92" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H92" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C93" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H93" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C94" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H94" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C95" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H95" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C96" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H96" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C97" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H97" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C98" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H98" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C99" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H99" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C100" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H100" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C101" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H101" r:id="rId172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C102" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H102" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C103" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H103" r:id="rId176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C104" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H104" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C105" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H105" r:id="rId180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C108" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H108" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C109" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H109" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C110" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H110" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C111" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H111" r:id="rId188"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C112" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H112" r:id="rId190"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C113" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H113" r:id="rId192"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C114" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H114" r:id="rId194"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C115" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H115" r:id="rId196"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C116" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H116" r:id="rId198"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C117" r:id="rId199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H117" r:id="rId200"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C118" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H118" r:id="rId202"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C119" r:id="rId203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H119" r:id="rId204"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C120" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H120" r:id="rId206"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C121" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H121" r:id="rId208"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C122" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H122" r:id="rId210"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C123" r:id="rId211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H123" r:id="rId212"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C124" r:id="rId213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H124" r:id="rId214"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C125" r:id="rId215"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H125" r:id="rId216"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C126" r:id="rId217"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H126" r:id="rId218"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C127" r:id="rId219"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H127" r:id="rId220"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C129" r:id="rId221"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H129" r:id="rId222"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C130" r:id="rId223"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H130" r:id="rId224"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C131" r:id="rId225"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H131" r:id="rId226"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C132" r:id="rId227"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H132" r:id="rId228"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C133" r:id="rId229"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H133" r:id="rId230"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C134" r:id="rId231"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H134" r:id="rId232"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C135" r:id="rId233"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H135" r:id="rId234"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C136" r:id="rId235"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H136" r:id="rId236"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C137" r:id="rId237"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H137" r:id="rId238"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C138" r:id="rId239"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H138" r:id="rId240"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C139" r:id="rId241"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H139" r:id="rId242"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C140" r:id="rId243"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H140" r:id="rId244"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C141" r:id="rId245"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H141" r:id="rId246"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C142" r:id="rId247"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H142" r:id="rId248"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C143" r:id="rId249"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H143" r:id="rId250"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C144" r:id="rId251"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H144" r:id="rId252"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C145" r:id="rId253"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H145" r:id="rId254"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C147" r:id="rId255"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H147" r:id="rId256"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C148" r:id="rId257"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H148" r:id="rId258"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C149" r:id="rId259"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H149" r:id="rId260"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C150" r:id="rId261"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H150" r:id="rId262"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C152" r:id="rId263"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H152" r:id="rId264"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C153" r:id="rId265"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H153" r:id="rId266"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C154" r:id="rId267"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H154" r:id="rId268"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C155" r:id="rId269"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H155" r:id="rId270"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C156" r:id="rId271"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H156" r:id="rId272"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C157" r:id="rId273"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H157" r:id="rId274"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C158" r:id="rId275"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H158" r:id="rId276"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C159" r:id="rId277"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H159" r:id="rId278"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C160" r:id="rId279"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H160" r:id="rId280"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C161" r:id="rId281"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H161" r:id="rId282"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C162" r:id="rId283"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H162" r:id="rId284"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C163" r:id="rId285"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H163" r:id="rId286"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C164" r:id="rId287"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H164" r:id="rId288"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C165" r:id="rId289"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H165" r:id="rId290"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C166" r:id="rId291"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H166" r:id="rId292"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C167" r:id="rId293"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H167" r:id="rId294"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C168" r:id="rId295"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H168" r:id="rId296"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C169" r:id="rId297"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H169" r:id="rId298"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C170" r:id="rId299"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H170" r:id="rId300"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C171" r:id="rId301"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H171" r:id="rId302"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C172" r:id="rId303"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H172" r:id="rId304"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C173" r:id="rId305"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H173" r:id="rId306"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C174" r:id="rId307"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H174" r:id="rId308"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C175" r:id="rId309"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H175" r:id="rId310"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C176" r:id="rId311"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H176" r:id="rId312"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C177" r:id="rId313"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H177" r:id="rId314"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C178" r:id="rId315"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H178" r:id="rId316"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C179" r:id="rId317"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H179" r:id="rId318"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C180" r:id="rId319"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H180" r:id="rId320"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C181" r:id="rId321"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H181" r:id="rId322"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C182" r:id="rId323"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H182" r:id="rId324"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C183" r:id="rId325"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H183" r:id="rId326"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C184" r:id="rId327"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H184" r:id="rId328"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C185" r:id="rId329"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H185" r:id="rId330"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C186" r:id="rId331"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H186" r:id="rId332"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C187" r:id="rId333"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H187" r:id="rId334"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C188" r:id="rId335"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H188" r:id="rId336"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C189" r:id="rId337"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H189" r:id="rId338"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C190" r:id="rId339"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H190" r:id="rId340"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C191" r:id="rId341"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H191" r:id="rId342"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C192" r:id="rId343"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H192" r:id="rId344"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C193" r:id="rId345"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H193" r:id="rId346"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C194" r:id="rId347"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H194" r:id="rId348"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C195" r:id="rId349"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H195" r:id="rId350"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C196" r:id="rId351"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H196" r:id="rId352"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C197" r:id="rId353"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H197" r:id="rId354"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C198" r:id="rId355"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H198" r:id="rId356"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C199" r:id="rId357"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H199" r:id="rId358"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C200" r:id="rId359"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H200" r:id="rId360"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C201" r:id="rId361"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H201" r:id="rId362"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C203" r:id="rId363"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H203" r:id="rId364"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C204" r:id="rId365"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H204" r:id="rId366"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C205" r:id="rId367"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H205" r:id="rId368"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C206" r:id="rId369"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H206" r:id="rId370"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C208" r:id="rId371"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H208" r:id="rId372"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C209" r:id="rId373"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H209" r:id="rId374"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C210" r:id="rId375"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H210" r:id="rId376"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C211" r:id="rId377"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H211" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H28" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H29" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H30" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H32" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C34" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C35" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C38" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C39" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H39" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C40" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H40" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C41" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H41" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C42" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H42" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C43" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H43" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C44" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H44" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C45" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H45" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C47" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H47" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C48" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H48" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C49" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H49" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C50" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H50" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C51" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H51" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C52" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H52" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C53" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H53" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C54" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H54" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C55" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H55" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C56" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H56" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C57" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H57" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C58" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H58" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C59" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H59" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C60" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H60" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C61" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H61" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C62" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H62" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C63" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H63" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C64" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H64" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C66" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H66" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C68" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H68" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C69" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H69" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C70" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H70" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C71" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H71" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C73" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H73" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C74" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H74" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C76" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H76" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C77" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H77" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C78" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H78" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C79" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H79" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C80" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H80" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C81" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H81" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C84" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H84" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C85" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H85" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C86" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H86" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C87" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H87" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C88" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H88" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C89" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H89" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C90" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H90" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C91" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H91" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C92" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H92" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C93" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H93" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C94" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H94" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C95" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H95" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C96" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H96" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C97" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H97" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C98" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H98" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C99" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H99" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C100" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H100" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C101" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H101" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C102" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H102" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C103" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H103" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C104" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H104" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C107" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H107" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C108" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H108" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C109" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H109" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C110" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H110" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C111" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H111" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C112" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H112" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C113" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H113" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C114" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H114" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C115" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H115" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C116" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H116" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C117" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H117" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C118" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H118" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C119" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H119" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C120" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H120" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C121" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H121" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C122" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H122" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C123" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H123" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C124" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H124" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C125" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H125" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C126" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H126" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C128" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H128" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C129" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H129" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C130" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H130" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C131" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H131" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C132" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H132" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C133" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H133" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C134" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H134" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C135" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H135" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C136" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H136" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C137" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H137" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C138" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H138" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C139" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H139" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C140" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H140" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C141" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H141" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C142" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H142" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C143" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H143" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C144" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H144" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C146" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H146" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C147" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H147" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C148" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H148" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C149" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H149" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C151" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H151" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C152" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H152" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C153" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H153" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C154" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H154" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C155" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H155" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C156" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H156" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C157" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H157" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C158" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H158" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C159" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H159" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C160" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H160" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C161" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H161" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C162" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H162" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C163" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H163" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C164" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H164" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C165" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H165" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C166" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H166" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C167" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H167" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C168" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H168" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C169" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H169" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C170" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H170" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C171" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H171" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C172" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H172" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C173" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H173" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C174" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H174" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C175" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H175" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C176" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H176" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C177" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H177" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C178" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H178" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C179" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H179" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C180" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H180" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C181" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H181" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C182" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H182" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C183" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H183" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C184" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H184" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C185" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H185" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C186" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H186" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C187" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H187" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C188" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H188" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C189" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H189" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C190" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H190" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C191" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H191" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C192" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H192" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C193" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H193" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C194" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H194" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C195" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H195" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C196" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H196" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C197" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H197" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C198" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H198" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C199" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H199" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C200" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H200" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C202" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H202" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C203" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H203" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C204" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H204" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C205" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H205" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C207" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H207" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C208" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H208" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C209" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H209" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C210" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H210" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C211" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H211" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C212" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H212" r:id="rId378"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
